--- a/scripts/data/Quality_parameters_v15042026.xlsx
+++ b/scripts/data/Quality_parameters_v15042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daan\Documents\GitHub\Website_Open_Topography_EU\scripts\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52271A14-FD12-4B25-A505-272C5081E28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE7D7B2-9169-4233-B469-8D6490F53BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{4BC1C8BB-35EF-4D62-B165-EB1ACD4AD7A7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2442" uniqueCount="779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2440" uniqueCount="778">
   <si>
     <t>ADM</t>
   </si>
@@ -814,10 +814,6 @@
   </si>
   <si>
     <t>https://www.ancpi.ro/laki3/en/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The European Economic Area (EEA) and Norway Grants, together with the National Agency of Cadastre and Land Registration Romania, funded the aerial point cloud datasets in Romania, i.e. the Laki2 and Laki3. The variation between the datasets is both in acquisition time and coverage. Both versions are available to academic users and public institutions. The data are acquired from the Krasovski 1940 ellipsoid, using the Stereographic 1970 projection (EPSG: 3844), and the elevation is referenced to the 1975 Black Sea normal height system (National Centre for Cartography, 2023). 
-According to the questionnaire, available specifications, and the web portal, neither dataset has national coverage. They cover different zones. The Laki2 is available in Arad, Bihor, Hunedoara, Alba, Mureș and Harghita, Caraș-Severin, Gorj, Mehedinți, and Dolj counties, while the Laki3 is available in Suceava, Neamț, Bacău, and Vrancea counties. These are shown in the overview of Figure 16, where the transparent grey represents the region acquired in the Laki2 acquisition campaign, orange indicates the Laki3 acquisition area, and purple outlines the country of Romania. </t>
   </si>
   <si>
     <t>Caraș-Severin</t>
@@ -3236,19 +3232,19 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>3</v>
@@ -3263,22 +3259,22 @@
         <v>6</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="P1" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>351</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>8</v>
@@ -3302,88 +3298,88 @@
         <v>14</v>
       </c>
       <c r="AA1" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="AB1" s="1" t="s">
         <v>356</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>357</v>
       </c>
       <c r="AC1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="AD1" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="AE1" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>369</v>
       </c>
       <c r="AF1" s="16" t="s">
         <v>16</v>
       </c>
       <c r="AG1" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="AI1" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="AJ1" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="AH1" s="1" t="s">
-        <v>716</v>
-      </c>
-      <c r="AI1" s="26" t="s">
-        <v>283</v>
-      </c>
-      <c r="AJ1" s="26" t="s">
+      <c r="AK1" s="26" t="s">
+        <v>284</v>
+      </c>
+      <c r="AL1" s="26" t="s">
+        <v>285</v>
+      </c>
+      <c r="AM1" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="AN1" s="26" t="s">
         <v>301</v>
       </c>
-      <c r="AK1" s="26" t="s">
-        <v>285</v>
-      </c>
-      <c r="AL1" s="26" t="s">
-        <v>286</v>
-      </c>
-      <c r="AM1" s="26" t="s">
-        <v>287</v>
-      </c>
-      <c r="AN1" s="26" t="s">
+      <c r="AO1" s="26" t="s">
         <v>302</v>
       </c>
-      <c r="AO1" s="26" t="s">
+      <c r="AP1" s="26" t="s">
         <v>303</v>
       </c>
-      <c r="AP1" s="26" t="s">
+      <c r="AQ1" s="26" t="s">
+        <v>288</v>
+      </c>
+      <c r="AR1" s="26" t="s">
         <v>304</v>
       </c>
-      <c r="AQ1" s="26" t="s">
-        <v>289</v>
-      </c>
-      <c r="AR1" s="26" t="s">
+      <c r="AS1" s="26" t="s">
         <v>305</v>
       </c>
-      <c r="AS1" s="26" t="s">
+      <c r="AT1" s="26" t="s">
         <v>306</v>
       </c>
-      <c r="AT1" s="26" t="s">
+      <c r="AU1" s="26" t="s">
         <v>307</v>
       </c>
-      <c r="AU1" s="26" t="s">
+      <c r="AV1" s="26" t="s">
         <v>308</v>
       </c>
-      <c r="AV1" s="26" t="s">
+      <c r="AW1" s="26" t="s">
         <v>309</v>
       </c>
-      <c r="AW1" s="26" t="s">
+      <c r="AX1" s="26" t="s">
         <v>310</v>
       </c>
-      <c r="AX1" s="26" t="s">
+      <c r="AY1" s="26" t="s">
         <v>311</v>
       </c>
-      <c r="AY1" s="26" t="s">
+      <c r="AZ1" s="26" t="s">
         <v>312</v>
       </c>
-      <c r="AZ1" s="26" t="s">
+      <c r="BA1" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="BA1" s="26" t="s">
-        <v>314</v>
-      </c>
       <c r="BB1" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2" spans="1:54" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3572,13 +3568,13 @@
         <v>24</v>
       </c>
       <c r="F5" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H5" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="I5" s="4">
         <v>0</v>
@@ -3587,10 +3583,10 @@
         <v>25</v>
       </c>
       <c r="K5" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>318</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>319</v>
       </c>
       <c r="M5" t="s">
         <v>26</v>
@@ -3629,7 +3625,7 @@
         <v>28</v>
       </c>
       <c r="AE5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AF5" s="4" t="s">
         <v>29</v>
@@ -3649,13 +3645,13 @@
         <v>24</v>
       </c>
       <c r="F6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H6" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="I6" s="4">
         <v>1</v>
@@ -3664,16 +3660,16 @@
         <v>25</v>
       </c>
       <c r="K6" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>318</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>319</v>
       </c>
       <c r="M6" t="s">
         <v>26</v>
       </c>
       <c r="O6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="U6">
         <v>15</v>
@@ -3706,7 +3702,7 @@
         <v>28</v>
       </c>
       <c r="AE6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AF6" s="4" t="s">
         <v>29</v>
@@ -3726,13 +3722,13 @@
         <v>24</v>
       </c>
       <c r="F7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="I7" s="4">
         <v>2</v>
@@ -3741,16 +3737,16 @@
         <v>25</v>
       </c>
       <c r="K7" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>318</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>319</v>
       </c>
       <c r="M7" t="s">
         <v>26</v>
       </c>
       <c r="O7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="U7">
         <v>15</v>
@@ -3780,10 +3776,10 @@
         <v>27</v>
       </c>
       <c r="AD7" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="AE7" t="s">
         <v>316</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>317</v>
       </c>
       <c r="AF7" s="4" t="s">
         <v>29</v>
@@ -3913,10 +3909,10 @@
         <v>34</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H10" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I10" s="4">
         <v>2</v>
@@ -3929,10 +3925,10 @@
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s">
+        <v>342</v>
+      </c>
+      <c r="N10" t="s">
         <v>343</v>
-      </c>
-      <c r="N10" t="s">
-        <v>344</v>
       </c>
       <c r="O10" t="s">
         <v>35</v>
@@ -3944,10 +3940,10 @@
         <v>1</v>
       </c>
       <c r="R10" t="s">
+        <v>351</v>
+      </c>
+      <c r="S10" t="s">
         <v>352</v>
-      </c>
-      <c r="S10" t="s">
-        <v>353</v>
       </c>
       <c r="V10" t="str">
         <f>IF(NOT(ISBLANK(T10)), IF(T10&gt;=AVERAGE($T$2:$T$124), 1, 0), IF(NOT(ISBLANK(U10)), IF(U10&gt;=AVERAGE($U$2:$U$124), 1, 0), "geen data"))</f>
@@ -3974,7 +3970,7 @@
         <v>27</v>
       </c>
       <c r="AD10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AE10" s="10" t="s">
         <v>36</v>
@@ -4000,10 +3996,10 @@
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H11" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I11" s="4">
         <v>1</v>
@@ -4012,16 +4008,16 @@
         <v>25</v>
       </c>
       <c r="K11" t="s">
+        <v>345</v>
+      </c>
+      <c r="L11" t="s">
         <v>346</v>
       </c>
-      <c r="L11" t="s">
-        <v>347</v>
-      </c>
       <c r="M11" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="N11" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O11" t="s">
         <v>35</v>
@@ -4069,10 +4065,10 @@
         <v>2010</v>
       </c>
       <c r="AD11" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AE11" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AF11" s="4" t="s">
         <v>37</v>
@@ -4095,10 +4091,10 @@
         <v>60</v>
       </c>
       <c r="G12" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H12" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I12" s="4">
         <v>2</v>
@@ -4107,16 +4103,16 @@
         <v>25</v>
       </c>
       <c r="K12" t="s">
+        <v>345</v>
+      </c>
+      <c r="L12" t="s">
         <v>346</v>
       </c>
-      <c r="L12" t="s">
-        <v>347</v>
-      </c>
       <c r="M12" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="N12" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O12" t="s">
         <v>35</v>
@@ -4161,10 +4157,10 @@
         <v>2023</v>
       </c>
       <c r="AD12" s="10" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AE12" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AF12" s="4" t="s">
         <v>37</v>
@@ -4184,10 +4180,10 @@
         <v>40</v>
       </c>
       <c r="G13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H13" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I13">
         <v>1</v>
@@ -4196,14 +4192,14 @@
         <v>25</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" t="s">
         <v>39</v>
       </c>
       <c r="N13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O13" t="s">
         <v>35</v>
@@ -4233,7 +4229,7 @@
         <v>2015</v>
       </c>
       <c r="AD13" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AE13" s="10" t="s">
         <v>41</v>
@@ -4256,10 +4252,10 @@
         <v>40</v>
       </c>
       <c r="G14" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H14" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I14">
         <v>2</v>
@@ -4268,14 +4264,14 @@
         <v>25</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" t="s">
         <v>39</v>
       </c>
       <c r="N14" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O14" t="s">
         <v>35</v>
@@ -4305,7 +4301,7 @@
         <v>2023</v>
       </c>
       <c r="AD14" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AE14" s="10" t="s">
         <v>41</v>
@@ -4328,13 +4324,13 @@
         <v>42</v>
       </c>
       <c r="E15" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G15" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H15" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I15" s="4">
         <v>1</v>
@@ -4350,7 +4346,7 @@
         <v>39</v>
       </c>
       <c r="N15" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O15" t="s">
         <v>35</v>
@@ -4392,10 +4388,10 @@
         <v>2021</v>
       </c>
       <c r="AD15" t="s">
+        <v>361</v>
+      </c>
+      <c r="AE15" s="10" t="s">
         <v>362</v>
-      </c>
-      <c r="AE15" s="10" t="s">
-        <v>363</v>
       </c>
       <c r="AF15" t="s">
         <v>37</v>
@@ -4468,7 +4464,7 @@
         <v>44</v>
       </c>
       <c r="H17" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I17" s="4">
         <v>1</v>
@@ -4605,13 +4601,13 @@
         <v>49</v>
       </c>
       <c r="E20" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G20" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H20" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I20" s="4">
         <v>1</v>
@@ -4666,13 +4662,13 @@
         <v>53</v>
       </c>
       <c r="F21" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H21" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I21">
         <v>1</v>
@@ -4685,10 +4681,10 @@
       </c>
       <c r="L21" s="2"/>
       <c r="M21" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="N21" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O21" t="s">
         <v>35</v>
@@ -4730,10 +4726,10 @@
         <v>2004</v>
       </c>
       <c r="AD21" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AE21" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AF21" s="2" t="s">
         <v>54</v>
@@ -4743,14 +4739,14 @@
       </c>
       <c r="AH21" s="2"/>
       <c r="AI21" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AJ21" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AN21" s="27"/>
       <c r="AQ21" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="22" spans="1:53" x14ac:dyDescent="0.25">
@@ -4767,13 +4763,13 @@
         <v>53</v>
       </c>
       <c r="F22" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H22" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -4786,10 +4782,10 @@
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="N22" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O22" t="s">
         <v>35</v>
@@ -4831,10 +4827,10 @@
         <v>2015</v>
       </c>
       <c r="AD22" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AE22" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AF22" s="2" t="s">
         <v>54</v>
@@ -4844,13 +4840,13 @@
       </c>
       <c r="AH22" s="2"/>
       <c r="AI22" t="s">
+        <v>273</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>279</v>
+      </c>
+      <c r="AQ22" t="s">
         <v>274</v>
-      </c>
-      <c r="AJ22" t="s">
-        <v>280</v>
-      </c>
-      <c r="AQ22" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="23" spans="1:53" x14ac:dyDescent="0.25">
@@ -4867,13 +4863,13 @@
         <v>55</v>
       </c>
       <c r="F23" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G23" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H23" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I23">
         <v>1</v>
@@ -4916,10 +4912,10 @@
         <v>2022</v>
       </c>
       <c r="AD23" t="s">
+        <v>329</v>
+      </c>
+      <c r="AE23" s="6" t="s">
         <v>330</v>
-      </c>
-      <c r="AE23" s="6" t="s">
-        <v>331</v>
       </c>
       <c r="AF23" s="2" t="s">
         <v>56</v>
@@ -4927,29 +4923,29 @@
       <c r="AG23" s="2"/>
       <c r="AH23" s="2"/>
       <c r="AI23" t="s">
+        <v>331</v>
+      </c>
+      <c r="AJ23" t="s">
         <v>332</v>
       </c>
-      <c r="AJ23" t="s">
+      <c r="AK23" t="s">
+        <v>276</v>
+      </c>
+      <c r="AL23" t="s">
         <v>333</v>
-      </c>
-      <c r="AK23" t="s">
-        <v>277</v>
-      </c>
-      <c r="AL23" t="s">
-        <v>334</v>
       </c>
       <c r="AN23" s="27"/>
       <c r="AQ23" t="s">
+        <v>334</v>
+      </c>
+      <c r="AR23" t="s">
         <v>335</v>
       </c>
-      <c r="AR23" t="s">
+      <c r="AV23" t="s">
         <v>336</v>
       </c>
-      <c r="AV23" t="s">
-        <v>337</v>
-      </c>
       <c r="AX23" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="24" spans="1:53" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -5062,10 +5058,10 @@
         <v>59</v>
       </c>
       <c r="E26" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F26" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -5172,10 +5168,10 @@
         <v>64</v>
       </c>
       <c r="F28" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="G28" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -5234,10 +5230,10 @@
         <v>64</v>
       </c>
       <c r="F29" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="G29" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -5296,10 +5292,10 @@
         <v>68</v>
       </c>
       <c r="F30" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="G30" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -5355,37 +5351,37 @@
       <c r="AG30" s="2"/>
       <c r="AH30" s="2"/>
       <c r="AI30" s="27" t="s">
+        <v>278</v>
+      </c>
+      <c r="AJ30" s="27" t="s">
         <v>279</v>
       </c>
-      <c r="AJ30" s="27" t="s">
-        <v>280</v>
-      </c>
       <c r="AK30" s="27" t="s">
+        <v>553</v>
+      </c>
+      <c r="AL30" s="27" t="s">
         <v>554</v>
       </c>
-      <c r="AL30" s="27" t="s">
+      <c r="AM30" t="s">
         <v>555</v>
-      </c>
-      <c r="AM30" t="s">
-        <v>556</v>
       </c>
       <c r="AN30" s="27"/>
       <c r="AO30" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AP30" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AQ30" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AV30" s="27"/>
       <c r="AW30" s="27"/>
       <c r="AX30" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="BA30" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="31" spans="1:53" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5402,7 +5398,7 @@
         <v>73</v>
       </c>
       <c r="F31" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -5464,31 +5460,31 @@
       <c r="AG31" s="2"/>
       <c r="AH31" s="2"/>
       <c r="AI31" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AJ31" s="27" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AK31" s="27"/>
       <c r="AM31" t="s">
+        <v>558</v>
+      </c>
+      <c r="AO31" t="s">
+        <v>283</v>
+      </c>
+      <c r="AP31" t="s">
         <v>559</v>
       </c>
-      <c r="AO31" t="s">
-        <v>284</v>
-      </c>
-      <c r="AP31" t="s">
-        <v>560</v>
-      </c>
       <c r="AQ31" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AV31" s="27"/>
       <c r="AW31" s="27"/>
       <c r="AX31" t="s">
+        <v>560</v>
+      </c>
+      <c r="BA31" t="s">
         <v>561</v>
-      </c>
-      <c r="BA31" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="32" spans="1:53" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5505,7 +5501,7 @@
         <v>73</v>
       </c>
       <c r="F32" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -5567,31 +5563,31 @@
       <c r="AG32" s="2"/>
       <c r="AH32" s="2"/>
       <c r="AI32" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AJ32" s="27" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AK32" s="27"/>
       <c r="AM32" t="s">
+        <v>558</v>
+      </c>
+      <c r="AO32" t="s">
+        <v>283</v>
+      </c>
+      <c r="AP32" t="s">
         <v>559</v>
       </c>
-      <c r="AO32" t="s">
-        <v>284</v>
-      </c>
-      <c r="AP32" t="s">
-        <v>560</v>
-      </c>
       <c r="AQ32" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AV32" s="27"/>
       <c r="AW32" s="27"/>
       <c r="AX32" t="s">
+        <v>560</v>
+      </c>
+      <c r="BA32" t="s">
         <v>561</v>
-      </c>
-      <c r="BA32" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="33" spans="1:62" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5608,7 +5604,7 @@
         <v>73</v>
       </c>
       <c r="F33" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -5670,31 +5666,31 @@
       <c r="AG33" s="2"/>
       <c r="AH33" s="2"/>
       <c r="AI33" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AJ33" s="27" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AK33" s="27"/>
       <c r="AM33" t="s">
+        <v>558</v>
+      </c>
+      <c r="AO33" t="s">
+        <v>283</v>
+      </c>
+      <c r="AP33" t="s">
         <v>559</v>
       </c>
-      <c r="AO33" t="s">
-        <v>284</v>
-      </c>
-      <c r="AP33" t="s">
-        <v>560</v>
-      </c>
       <c r="AQ33" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AV33" s="27"/>
       <c r="AW33" s="27"/>
       <c r="AX33" t="s">
+        <v>560</v>
+      </c>
+      <c r="BA33" t="s">
         <v>561</v>
-      </c>
-      <c r="BA33" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="34" spans="1:62" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5711,7 +5707,7 @@
         <v>73</v>
       </c>
       <c r="F34" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -5773,31 +5769,31 @@
       <c r="AG34" s="2"/>
       <c r="AH34" s="2"/>
       <c r="AI34" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AJ34" s="27" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AK34" s="27"/>
       <c r="AM34" t="s">
+        <v>558</v>
+      </c>
+      <c r="AO34" t="s">
+        <v>283</v>
+      </c>
+      <c r="AP34" t="s">
         <v>559</v>
       </c>
-      <c r="AO34" t="s">
-        <v>284</v>
-      </c>
-      <c r="AP34" t="s">
-        <v>560</v>
-      </c>
       <c r="AQ34" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AV34" s="27"/>
       <c r="AW34" s="27"/>
       <c r="AX34" t="s">
+        <v>560</v>
+      </c>
+      <c r="BA34" t="s">
         <v>561</v>
-      </c>
-      <c r="BA34" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="35" spans="1:62" x14ac:dyDescent="0.25">
@@ -5814,34 +5810,34 @@
         <v>152</v>
       </c>
       <c r="H35" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="I35">
         <v>1</v>
       </c>
       <c r="AI35" t="s">
+        <v>282</v>
+      </c>
+      <c r="AJ35" t="s">
+        <v>557</v>
+      </c>
+      <c r="AM35" t="s">
+        <v>558</v>
+      </c>
+      <c r="AO35" t="s">
         <v>283</v>
       </c>
-      <c r="AJ35" t="s">
-        <v>558</v>
-      </c>
-      <c r="AM35" t="s">
+      <c r="AP35" t="s">
         <v>559</v>
       </c>
-      <c r="AO35" t="s">
-        <v>284</v>
-      </c>
-      <c r="AP35" t="s">
+      <c r="AQ35" t="s">
+        <v>274</v>
+      </c>
+      <c r="AX35" t="s">
         <v>560</v>
       </c>
-      <c r="AQ35" t="s">
-        <v>275</v>
-      </c>
-      <c r="AX35" t="s">
+      <c r="BA35" t="s">
         <v>561</v>
-      </c>
-      <c r="BA35" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="36" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5858,7 +5854,7 @@
         <v>78</v>
       </c>
       <c r="F36" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -5879,7 +5875,7 @@
         <v>26</v>
       </c>
       <c r="N36" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O36" t="s">
         <v>35</v>
@@ -5917,46 +5913,46 @@
       <c r="AG36" s="2"/>
       <c r="AH36" s="2"/>
       <c r="AI36" s="27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AJ36" s="27" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AK36" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AL36" s="27" t="s">
+        <v>562</v>
+      </c>
+      <c r="AM36" t="s">
         <v>563</v>
       </c>
-      <c r="AM36" t="s">
+      <c r="AP36" t="s">
         <v>564</v>
       </c>
-      <c r="AP36" t="s">
+      <c r="AQ36" s="27" t="s">
         <v>565</v>
       </c>
-      <c r="AQ36" s="27" t="s">
+      <c r="AR36" t="s">
         <v>566</v>
       </c>
-      <c r="AR36" t="s">
+      <c r="AT36" s="27" t="s">
         <v>567</v>
       </c>
-      <c r="AT36" s="27" t="s">
+      <c r="AU36" s="27" t="s">
         <v>568</v>
       </c>
-      <c r="AU36" s="27" t="s">
+      <c r="AV36" s="27" t="s">
         <v>569</v>
       </c>
-      <c r="AV36" s="27" t="s">
+      <c r="AW36" t="s">
         <v>570</v>
       </c>
-      <c r="AW36" t="s">
+      <c r="AX36" t="s">
         <v>571</v>
       </c>
-      <c r="AX36" t="s">
+      <c r="BA36" t="s">
         <v>572</v>
-      </c>
-      <c r="BA36" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="37" spans="1:62" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5973,7 +5969,7 @@
         <v>78</v>
       </c>
       <c r="F37" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -5994,7 +5990,7 @@
         <v>26</v>
       </c>
       <c r="N37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O37" t="s">
         <v>35</v>
@@ -6032,46 +6028,46 @@
       <c r="AG37" s="2"/>
       <c r="AH37" s="2"/>
       <c r="AI37" s="27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AJ37" s="27" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AK37" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AL37" s="27" t="s">
+        <v>562</v>
+      </c>
+      <c r="AM37" t="s">
         <v>563</v>
       </c>
-      <c r="AM37" t="s">
+      <c r="AP37" t="s">
         <v>564</v>
       </c>
-      <c r="AP37" t="s">
+      <c r="AQ37" s="27" t="s">
         <v>565</v>
       </c>
-      <c r="AQ37" s="27" t="s">
+      <c r="AR37" t="s">
         <v>566</v>
       </c>
-      <c r="AR37" t="s">
+      <c r="AT37" s="27" t="s">
         <v>567</v>
       </c>
-      <c r="AT37" s="27" t="s">
+      <c r="AU37" s="27" t="s">
         <v>568</v>
       </c>
-      <c r="AU37" s="27" t="s">
+      <c r="AV37" s="27" t="s">
         <v>569</v>
       </c>
-      <c r="AV37" s="27" t="s">
+      <c r="AW37" t="s">
         <v>570</v>
       </c>
-      <c r="AW37" t="s">
+      <c r="AX37" t="s">
         <v>571</v>
       </c>
-      <c r="AX37" t="s">
+      <c r="BA37" t="s">
         <v>572</v>
-      </c>
-      <c r="BA37" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="38" spans="1:62" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6088,7 +6084,7 @@
         <v>83</v>
       </c>
       <c r="F38" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -6109,7 +6105,7 @@
         <v>26</v>
       </c>
       <c r="N38" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O38" t="s">
         <v>35</v>
@@ -6145,31 +6141,31 @@
         <v>87</v>
       </c>
       <c r="AI38" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AJ38" t="s">
+        <v>279</v>
+      </c>
+      <c r="AK38" t="s">
+        <v>284</v>
+      </c>
+      <c r="AL38" t="s">
+        <v>285</v>
+      </c>
+      <c r="AM38" t="s">
+        <v>286</v>
+      </c>
+      <c r="AO38" t="s">
         <v>280</v>
       </c>
-      <c r="AK38" t="s">
-        <v>285</v>
-      </c>
-      <c r="AL38" t="s">
-        <v>286</v>
-      </c>
-      <c r="AM38" t="s">
-        <v>287</v>
-      </c>
-      <c r="AO38" t="s">
-        <v>281</v>
-      </c>
       <c r="AQ38" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AX38" t="s">
+        <v>573</v>
+      </c>
+      <c r="BA38" t="s">
         <v>574</v>
-      </c>
-      <c r="BA38" t="s">
-        <v>575</v>
       </c>
       <c r="BG38" s="2"/>
       <c r="BI38" s="3"/>
@@ -6189,7 +6185,7 @@
         <v>83</v>
       </c>
       <c r="F39" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -6210,7 +6206,7 @@
         <v>26</v>
       </c>
       <c r="N39" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O39" t="s">
         <v>35</v>
@@ -6246,31 +6242,31 @@
         <v>87</v>
       </c>
       <c r="AI39" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AJ39" t="s">
+        <v>279</v>
+      </c>
+      <c r="AK39" t="s">
+        <v>284</v>
+      </c>
+      <c r="AL39" t="s">
+        <v>285</v>
+      </c>
+      <c r="AM39" t="s">
+        <v>286</v>
+      </c>
+      <c r="AO39" t="s">
         <v>280</v>
       </c>
-      <c r="AK39" t="s">
-        <v>285</v>
-      </c>
-      <c r="AL39" t="s">
-        <v>286</v>
-      </c>
-      <c r="AM39" t="s">
-        <v>287</v>
-      </c>
-      <c r="AO39" t="s">
-        <v>281</v>
-      </c>
       <c r="AQ39" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AX39" t="s">
+        <v>573</v>
+      </c>
+      <c r="BA39" t="s">
         <v>574</v>
-      </c>
-      <c r="BA39" t="s">
-        <v>575</v>
       </c>
       <c r="BG39" s="2"/>
       <c r="BI39" s="3"/>
@@ -6290,7 +6286,7 @@
         <v>88</v>
       </c>
       <c r="F40" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -6311,7 +6307,7 @@
         <v>26</v>
       </c>
       <c r="N40" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O40" t="s">
         <v>35</v>
@@ -6344,34 +6340,34 @@
         <v>91</v>
       </c>
       <c r="AI40" t="s">
+        <v>282</v>
+      </c>
+      <c r="AJ40" t="s">
+        <v>279</v>
+      </c>
+      <c r="AK40" t="s">
+        <v>284</v>
+      </c>
+      <c r="AL40" t="s">
+        <v>285</v>
+      </c>
+      <c r="AM40" t="s">
+        <v>286</v>
+      </c>
+      <c r="AO40" t="s">
         <v>283</v>
       </c>
-      <c r="AJ40" t="s">
-        <v>280</v>
-      </c>
-      <c r="AK40" t="s">
-        <v>285</v>
-      </c>
-      <c r="AL40" t="s">
-        <v>286</v>
-      </c>
-      <c r="AM40" t="s">
-        <v>287</v>
-      </c>
-      <c r="AO40" t="s">
-        <v>284</v>
-      </c>
       <c r="AP40" t="s">
+        <v>575</v>
+      </c>
+      <c r="AQ40" t="s">
+        <v>274</v>
+      </c>
+      <c r="AX40" t="s">
+        <v>281</v>
+      </c>
+      <c r="BA40" t="s">
         <v>576</v>
-      </c>
-      <c r="AQ40" t="s">
-        <v>275</v>
-      </c>
-      <c r="AX40" t="s">
-        <v>282</v>
-      </c>
-      <c r="BA40" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="41" spans="1:62" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -6388,10 +6384,10 @@
         <v>92</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H41" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I41">
         <v>1</v>
@@ -6409,7 +6405,7 @@
         <v>26</v>
       </c>
       <c r="N41" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O41" t="s">
         <v>35</v>
@@ -6456,10 +6452,10 @@
         <v>94</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H42" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I42">
         <v>1</v>
@@ -6477,7 +6473,7 @@
         <v>39</v>
       </c>
       <c r="N42" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O42" t="s">
         <v>35</v>
@@ -6518,10 +6514,10 @@
         <v>95</v>
       </c>
       <c r="G43" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H43" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I43">
         <v>1</v>
@@ -6539,7 +6535,7 @@
         <v>26</v>
       </c>
       <c r="N43" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O43" t="s">
         <v>35</v>
@@ -6575,16 +6571,16 @@
         <v>37</v>
       </c>
       <c r="AI43" t="s">
+        <v>282</v>
+      </c>
+      <c r="AJ43" t="s">
+        <v>279</v>
+      </c>
+      <c r="AO43" t="s">
         <v>283</v>
       </c>
-      <c r="AJ43" t="s">
-        <v>280</v>
-      </c>
-      <c r="AO43" t="s">
-        <v>284</v>
-      </c>
       <c r="BA43" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="44" spans="1:62" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6601,16 +6597,16 @@
         <v>97</v>
       </c>
       <c r="E44" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="F44" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H44" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I44">
         <v>1</v>
@@ -6628,7 +6624,7 @@
         <v>26</v>
       </c>
       <c r="N44" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O44" t="s">
         <v>35</v>
@@ -6658,7 +6654,7 @@
         <v>2021</v>
       </c>
       <c r="AD44" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="AE44" s="6" t="s">
         <v>98</v>
@@ -6670,19 +6666,19 @@
       <c r="AH44" s="2"/>
       <c r="AI44" s="27"/>
       <c r="AJ44" s="27" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AK44" t="s">
+        <v>284</v>
+      </c>
+      <c r="AL44" s="27" t="s">
         <v>285</v>
       </c>
-      <c r="AL44" s="27" t="s">
+      <c r="AM44" t="s">
         <v>286</v>
       </c>
-      <c r="AM44" t="s">
-        <v>287</v>
-      </c>
       <c r="AP44" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="45" spans="1:62" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6699,13 +6695,13 @@
         <v>99</v>
       </c>
       <c r="E45" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="G45" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H45" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I45">
         <v>1</v>
@@ -6723,7 +6719,7 @@
         <v>26</v>
       </c>
       <c r="N45" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O45" t="s">
         <v>35</v>
@@ -6757,7 +6753,7 @@
         <v>100</v>
       </c>
       <c r="AE45" s="6" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="AF45" s="13" t="s">
         <v>37</v>
@@ -6777,13 +6773,13 @@
         <v>101</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H46" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -6801,7 +6797,7 @@
         <v>39</v>
       </c>
       <c r="N46" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O46" t="s">
         <v>35</v>
@@ -6834,7 +6830,7 @@
         <v>102</v>
       </c>
       <c r="AE46" s="6" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AF46" s="13" t="s">
         <v>37</v>
@@ -6854,10 +6850,10 @@
         <v>103</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H47" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I47">
         <v>1</v>
@@ -6875,7 +6871,7 @@
         <v>39</v>
       </c>
       <c r="N47" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O47" t="s">
         <v>35</v>
@@ -6905,34 +6901,34 @@
         <v>2021</v>
       </c>
       <c r="AD47" s="6" t="s">
+        <v>748</v>
+      </c>
+      <c r="AE47" s="6" t="s">
         <v>749</v>
-      </c>
-      <c r="AE47" s="6" t="s">
-        <v>750</v>
       </c>
       <c r="AF47" t="s">
         <v>37</v>
       </c>
       <c r="AI47" t="s">
+        <v>282</v>
+      </c>
+      <c r="AJ47" t="s">
+        <v>279</v>
+      </c>
+      <c r="AK47" t="s">
+        <v>579</v>
+      </c>
+      <c r="AL47" t="s">
+        <v>580</v>
+      </c>
+      <c r="AM47" t="s">
+        <v>581</v>
+      </c>
+      <c r="AO47" t="s">
         <v>283</v>
       </c>
-      <c r="AJ47" t="s">
-        <v>280</v>
-      </c>
-      <c r="AK47" t="s">
-        <v>580</v>
-      </c>
-      <c r="AL47" t="s">
-        <v>581</v>
-      </c>
-      <c r="AM47" t="s">
+      <c r="AP47" t="s">
         <v>582</v>
-      </c>
-      <c r="AO47" t="s">
-        <v>284</v>
-      </c>
-      <c r="AP47" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="48" spans="1:62" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6949,16 +6945,16 @@
         <v>104</v>
       </c>
       <c r="E48" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="F48" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="G48" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H48" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I48">
         <v>1</v>
@@ -6976,7 +6972,7 @@
         <v>26</v>
       </c>
       <c r="N48" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O48" t="s">
         <v>35</v>
@@ -7009,7 +7005,7 @@
         <v>105</v>
       </c>
       <c r="AE48" s="6" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="AF48" s="13" t="s">
         <v>37</v>
@@ -7029,10 +7025,10 @@
         <v>106</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H49" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I49">
         <v>1</v>
@@ -7083,25 +7079,25 @@
         <v>108</v>
       </c>
       <c r="AI49" t="s">
+        <v>583</v>
+      </c>
+      <c r="AJ49" t="s">
         <v>584</v>
       </c>
-      <c r="AJ49" t="s">
+      <c r="AQ49" t="s">
+        <v>288</v>
+      </c>
+      <c r="AX49" t="s">
+        <v>289</v>
+      </c>
+      <c r="AY49" t="s">
+        <v>290</v>
+      </c>
+      <c r="AZ49" t="s">
         <v>585</v>
       </c>
-      <c r="AQ49" t="s">
-        <v>289</v>
-      </c>
-      <c r="AX49" t="s">
-        <v>290</v>
-      </c>
-      <c r="AY49" t="s">
-        <v>291</v>
-      </c>
-      <c r="AZ49" t="s">
+      <c r="BA49" t="s">
         <v>586</v>
-      </c>
-      <c r="BA49" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="50" spans="1:53" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7118,13 +7114,13 @@
         <v>109</v>
       </c>
       <c r="F50" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H50" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I50">
         <v>1</v>
@@ -7142,7 +7138,7 @@
         <v>26</v>
       </c>
       <c r="N50" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O50" t="s">
         <v>35</v>
@@ -7175,7 +7171,7 @@
         <v>2024</v>
       </c>
       <c r="AD50" s="6" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AE50" s="17" t="s">
         <v>110</v>
@@ -7184,22 +7180,22 @@
         <v>37</v>
       </c>
       <c r="AI50" t="s">
+        <v>282</v>
+      </c>
+      <c r="AJ50" t="s">
+        <v>279</v>
+      </c>
+      <c r="AO50" t="s">
         <v>283</v>
       </c>
-      <c r="AJ50" t="s">
-        <v>280</v>
-      </c>
-      <c r="AO50" t="s">
-        <v>284</v>
-      </c>
       <c r="AQ50" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AU50" t="s">
+        <v>587</v>
+      </c>
+      <c r="BA50" t="s">
         <v>588</v>
-      </c>
-      <c r="BA50" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="51" spans="1:53" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7216,13 +7212,13 @@
         <v>111</v>
       </c>
       <c r="F51" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H51" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I51">
         <v>1</v>
@@ -7240,7 +7236,7 @@
         <v>26</v>
       </c>
       <c r="N51" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O51" t="s">
         <v>35</v>
@@ -7267,7 +7263,7 @@
         <v>2025</v>
       </c>
       <c r="AD51" s="6" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="AE51" s="6" t="s">
         <v>112</v>
@@ -7290,16 +7286,16 @@
         <v>113</v>
       </c>
       <c r="E52" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="F52" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H52" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I52">
         <v>1</v>
@@ -7317,7 +7313,7 @@
         <v>26</v>
       </c>
       <c r="N52" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O52" t="s">
         <v>35</v>
@@ -7347,7 +7343,7 @@
         <v>114</v>
       </c>
       <c r="AE52" s="6" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="AF52" s="13" t="s">
         <v>37</v>
@@ -7367,13 +7363,13 @@
         <v>115</v>
       </c>
       <c r="E53" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H53" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I53">
         <v>1</v>
@@ -7391,7 +7387,7 @@
         <v>26</v>
       </c>
       <c r="N53" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O53" t="s">
         <v>35</v>
@@ -7421,10 +7417,10 @@
         <v>2023</v>
       </c>
       <c r="AD53" s="6" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="AE53" s="6" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="AF53" t="s">
         <v>116</v>
@@ -7444,16 +7440,16 @@
         <v>117</v>
       </c>
       <c r="E54" s="30" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F54" s="30" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H54" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I54">
         <v>1</v>
@@ -7468,10 +7464,10 @@
         <v>90</v>
       </c>
       <c r="M54" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="N54" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O54" t="s">
         <v>35</v>
@@ -7480,7 +7476,7 @@
         <v>1</v>
       </c>
       <c r="S54" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="T54">
         <v>4</v>
@@ -7498,10 +7494,10 @@
         <v>geen data</v>
       </c>
       <c r="AD54" s="6" t="s">
+        <v>766</v>
+      </c>
+      <c r="AE54" s="6" t="s">
         <v>767</v>
-      </c>
-      <c r="AE54" s="6" t="s">
-        <v>768</v>
       </c>
       <c r="AF54" s="13" t="s">
         <v>116</v>
@@ -7521,13 +7517,13 @@
         <v>118</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H55" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I55">
         <v>1</v>
@@ -7545,7 +7541,7 @@
         <v>39</v>
       </c>
       <c r="N55" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O55" t="s">
         <v>35</v>
@@ -7578,7 +7574,7 @@
         <v>119</v>
       </c>
       <c r="AE55" s="6" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="AF55" s="13" t="s">
         <v>37</v>
@@ -7598,7 +7594,7 @@
         <v>120</v>
       </c>
       <c r="H56" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I56">
         <v>1</v>
@@ -7613,7 +7609,7 @@
         <v>90</v>
       </c>
       <c r="M56" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="N56" t="s">
         <v>61</v>
@@ -7661,10 +7657,10 @@
         <v>2013</v>
       </c>
       <c r="AD56" s="6" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="AE56" s="6" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="AF56" s="13" t="s">
         <v>37</v>
@@ -7684,7 +7680,7 @@
         <v>120</v>
       </c>
       <c r="H57" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I57">
         <v>2</v>
@@ -7699,7 +7695,7 @@
         <v>90</v>
       </c>
       <c r="M57" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="N57" t="s">
         <v>61</v>
@@ -7747,10 +7743,10 @@
         <v>2019</v>
       </c>
       <c r="AD57" s="6" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="AE57" s="6" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="AF57" s="13" t="s">
         <v>37</v>
@@ -7770,7 +7766,7 @@
         <v>120</v>
       </c>
       <c r="H58" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -7785,7 +7781,7 @@
         <v>90</v>
       </c>
       <c r="M58" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="N58" t="s">
         <v>61</v>
@@ -7833,10 +7829,10 @@
         <v>2025</v>
       </c>
       <c r="AD58" s="6" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="AE58" s="6" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="AF58" s="13" t="s">
         <v>37</v>
@@ -7883,7 +7879,7 @@
         <v>123</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C60" t="s">
         <v>121</v>
@@ -7892,7 +7888,7 @@
         <v>123</v>
       </c>
       <c r="H60" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="I60">
         <v>1</v>
@@ -7999,10 +7995,10 @@
         <v>129</v>
       </c>
       <c r="F62" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I62" s="5">
         <v>1</v>
@@ -8073,10 +8069,10 @@
         <v>132</v>
       </c>
       <c r="E63" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="F63" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -8123,19 +8119,19 @@
         <v>132</v>
       </c>
       <c r="B64" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C64" t="s">
         <v>132</v>
       </c>
       <c r="D64" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F64" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H64" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="I64">
         <v>1</v>
@@ -8185,7 +8181,7 @@
       <c r="E66" s="2"/>
       <c r="G66" s="2"/>
       <c r="H66" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I66" s="2"/>
       <c r="J66" t="s">
@@ -8244,7 +8240,7 @@
       <c r="E67" s="2"/>
       <c r="G67" s="2"/>
       <c r="H67" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I67" s="2"/>
       <c r="J67" t="s">
@@ -8294,7 +8290,7 @@
       <c r="E68" s="2"/>
       <c r="G68" s="2"/>
       <c r="H68" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I68" s="2"/>
       <c r="J68" t="s">
@@ -8449,7 +8445,7 @@
         <v>147</v>
       </c>
       <c r="F71" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -8505,20 +8501,20 @@
       <c r="AG71" s="2"/>
       <c r="AH71" s="2"/>
       <c r="AJ71" s="27" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AK71" s="27" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AM71" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AO71" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AT71" s="27"/>
       <c r="AV71" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="72" spans="1:56" x14ac:dyDescent="0.25">
@@ -8526,7 +8522,7 @@
         <v>152</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C72" t="s">
         <v>152</v>
@@ -8535,10 +8531,10 @@
         <v>152</v>
       </c>
       <c r="F72" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H72" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="I72">
         <v>1</v>
@@ -8593,10 +8589,10 @@
         <v>155</v>
       </c>
       <c r="F73" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H73" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I73">
         <v>1</v>
@@ -8638,22 +8634,22 @@
         <v>156</v>
       </c>
       <c r="AI73" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AJ73" t="s">
+        <v>279</v>
+      </c>
+      <c r="AK73" t="s">
+        <v>284</v>
+      </c>
+      <c r="AO73" t="s">
         <v>280</v>
       </c>
-      <c r="AK73" t="s">
-        <v>285</v>
-      </c>
-      <c r="AO73" t="s">
-        <v>281</v>
-      </c>
       <c r="AQ73" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AX73" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="74" spans="1:56" x14ac:dyDescent="0.25">
@@ -8670,7 +8666,7 @@
         <v>157</v>
       </c>
       <c r="F74" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -8729,29 +8725,29 @@
       <c r="AG74" s="2"/>
       <c r="AH74" s="2"/>
       <c r="AI74" s="27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AJ74" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="AK74" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="AL74" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="AM74" t="s">
+        <v>286</v>
+      </c>
+      <c r="AO74" t="s">
         <v>280</v>
       </c>
-      <c r="AK74" s="27" t="s">
-        <v>285</v>
-      </c>
-      <c r="AL74" s="27" t="s">
-        <v>286</v>
-      </c>
-      <c r="AM74" t="s">
-        <v>287</v>
-      </c>
-      <c r="AO74" t="s">
-        <v>281</v>
-      </c>
       <c r="AP74" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AQ74" s="27"/>
       <c r="BA74" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="75" spans="1:56" x14ac:dyDescent="0.25">
@@ -8768,7 +8764,7 @@
         <v>161</v>
       </c>
       <c r="F75" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -8821,39 +8817,39 @@
       <c r="AG75" s="2"/>
       <c r="AH75" s="2"/>
       <c r="AI75" s="27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AJ75" s="27" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AK75" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="AL75" s="27" t="s">
         <v>285</v>
       </c>
-      <c r="AL75" s="27" t="s">
+      <c r="AM75" t="s">
         <v>286</v>
-      </c>
-      <c r="AM75" t="s">
-        <v>287</v>
       </c>
       <c r="AN75" s="27"/>
       <c r="AO75" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AP75" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AQ75" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AR75" s="27"/>
       <c r="AT75" s="27" t="s">
+        <v>291</v>
+      </c>
+      <c r="AU75" t="s">
         <v>292</v>
       </c>
-      <c r="AU75" t="s">
+      <c r="AV75" t="s">
         <v>293</v>
-      </c>
-      <c r="AV75" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="76" spans="1:56" x14ac:dyDescent="0.25">
@@ -8870,7 +8866,7 @@
         <v>165</v>
       </c>
       <c r="F76" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -8920,29 +8916,29 @@
       <c r="AG76" s="2"/>
       <c r="AH76" s="2"/>
       <c r="AI76" s="27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AJ76" s="27" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AK76" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="AL76" s="27" t="s">
         <v>285</v>
       </c>
-      <c r="AL76" s="27" t="s">
+      <c r="AM76" t="s">
         <v>286</v>
-      </c>
-      <c r="AM76" t="s">
-        <v>287</v>
       </c>
       <c r="AN76" s="27"/>
       <c r="AO76" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AP76" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AQ76" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="77" spans="1:56" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -9103,13 +9099,13 @@
         <v>172</v>
       </c>
       <c r="E80" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F80" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G80" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -9127,10 +9123,10 @@
         <v>173</v>
       </c>
       <c r="M80" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="N80" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O80" t="s">
         <v>35</v>
@@ -9142,10 +9138,10 @@
         <v>1</v>
       </c>
       <c r="R80" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="S80" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="T80">
         <v>6</v>
@@ -9178,7 +9174,7 @@
         <v>2012</v>
       </c>
       <c r="AD80" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="AE80" t="s">
         <v>174</v>
@@ -9187,21 +9183,21 @@
         <v>175</v>
       </c>
       <c r="AJ80" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AK80" s="27"/>
       <c r="AO80" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AQ80" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AS80" s="27"/>
       <c r="AU80" t="s">
+        <v>592</v>
+      </c>
+      <c r="BA80" t="s">
         <v>593</v>
-      </c>
-      <c r="BA80" t="s">
-        <v>594</v>
       </c>
       <c r="BD80" s="27"/>
     </row>
@@ -9219,13 +9215,13 @@
         <v>172</v>
       </c>
       <c r="E81" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F81" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G81" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -9243,10 +9239,10 @@
         <v>173</v>
       </c>
       <c r="M81" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="N81" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O81" t="s">
         <v>35</v>
@@ -9258,10 +9254,10 @@
         <v>1</v>
       </c>
       <c r="R81" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="S81" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="T81">
         <v>6</v>
@@ -9294,7 +9290,7 @@
         <v>2019</v>
       </c>
       <c r="AD81" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="AE81" t="s">
         <v>174</v>
@@ -9303,21 +9299,21 @@
         <v>175</v>
       </c>
       <c r="AJ81" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AK81" s="27"/>
       <c r="AO81" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AQ81" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AS81" s="27"/>
       <c r="AU81" t="s">
+        <v>592</v>
+      </c>
+      <c r="BA81" t="s">
         <v>593</v>
-      </c>
-      <c r="BA81" t="s">
-        <v>594</v>
       </c>
       <c r="BD81" s="27"/>
     </row>
@@ -9335,13 +9331,13 @@
         <v>172</v>
       </c>
       <c r="E82" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F82" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G82" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -9359,10 +9355,10 @@
         <v>173</v>
       </c>
       <c r="M82" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="N82" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O82" t="s">
         <v>35</v>
@@ -9374,10 +9370,10 @@
         <v>1</v>
       </c>
       <c r="R82" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="S82" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="T82">
         <v>10</v>
@@ -9410,7 +9406,7 @@
         <v>2023</v>
       </c>
       <c r="AD82" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="AE82" t="s">
         <v>174</v>
@@ -9419,21 +9415,21 @@
         <v>175</v>
       </c>
       <c r="AJ82" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AK82" s="27"/>
       <c r="AO82" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AQ82" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AS82" s="27"/>
       <c r="AU82" t="s">
+        <v>592</v>
+      </c>
+      <c r="BA82" t="s">
         <v>593</v>
-      </c>
-      <c r="BA82" t="s">
-        <v>594</v>
       </c>
       <c r="BD82" s="27"/>
     </row>
@@ -9451,13 +9447,13 @@
         <v>172</v>
       </c>
       <c r="E83" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F83" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G83" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -9475,10 +9471,10 @@
         <v>173</v>
       </c>
       <c r="M83" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="N83" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O83" t="s">
         <v>35</v>
@@ -9490,10 +9486,10 @@
         <v>1</v>
       </c>
       <c r="R83" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="S83" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="T83">
         <v>10</v>
@@ -9526,7 +9522,7 @@
         <v>2024</v>
       </c>
       <c r="AD83" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="AE83" t="s">
         <v>174</v>
@@ -9535,21 +9531,21 @@
         <v>175</v>
       </c>
       <c r="AJ83" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AK83" s="27"/>
       <c r="AO83" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AQ83" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AS83" s="27"/>
       <c r="AU83" t="s">
+        <v>592</v>
+      </c>
+      <c r="BA83" t="s">
         <v>593</v>
-      </c>
-      <c r="BA83" t="s">
-        <v>594</v>
       </c>
       <c r="BD83" s="27"/>
     </row>
@@ -9567,13 +9563,13 @@
         <v>172</v>
       </c>
       <c r="E84" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F84" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G84" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -9591,10 +9587,10 @@
         <v>173</v>
       </c>
       <c r="M84" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="N84" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O84" t="s">
         <v>35</v>
@@ -9606,10 +9602,10 @@
         <v>1</v>
       </c>
       <c r="R84" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="S84" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="T84">
         <v>10</v>
@@ -9642,7 +9638,7 @@
         <v>2027</v>
       </c>
       <c r="AD84" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="AE84" t="s">
         <v>174</v>
@@ -9651,21 +9647,21 @@
         <v>175</v>
       </c>
       <c r="AJ84" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AK84" s="27"/>
       <c r="AO84" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AQ84" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AS84" s="27"/>
       <c r="AU84" t="s">
+        <v>592</v>
+      </c>
+      <c r="BA84" t="s">
         <v>593</v>
-      </c>
-      <c r="BA84" t="s">
-        <v>594</v>
       </c>
       <c r="BD84" s="27"/>
     </row>
@@ -9683,13 +9679,13 @@
         <v>172</v>
       </c>
       <c r="E85" t="s">
+        <v>378</v>
+      </c>
+      <c r="F85" t="s">
         <v>379</v>
       </c>
-      <c r="F85" t="s">
-        <v>380</v>
-      </c>
       <c r="G85" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -9710,13 +9706,13 @@
         <v>39</v>
       </c>
       <c r="O85" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P85">
         <v>1</v>
       </c>
       <c r="R85" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="U85">
         <v>25</v>
@@ -9740,7 +9736,7 @@
         <v>2021</v>
       </c>
       <c r="AE85" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="AF85" s="15" t="s">
         <v>175</v>
@@ -9751,28 +9747,28 @@
     </row>
     <row r="86" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C86" t="s">
         <v>172</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G86" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="I86" s="4">
         <v>1</v>
@@ -9822,7 +9818,7 @@
         <v>178</v>
       </c>
       <c r="E87" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -9867,7 +9863,7 @@
         <v>179</v>
       </c>
       <c r="AE87" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="AF87" t="s">
         <v>180</v>
@@ -9887,10 +9883,10 @@
         <v>181</v>
       </c>
       <c r="E88" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="F88" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -9935,10 +9931,10 @@
         <v>1</v>
       </c>
       <c r="AB88" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="AD88" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="AE88" t="s">
         <v>184</v>
@@ -9947,13 +9943,13 @@
         <v>185</v>
       </c>
       <c r="AI88" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AP88" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AQ88" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="89" spans="1:58" x14ac:dyDescent="0.25">
@@ -9970,10 +9966,10 @@
         <v>186</v>
       </c>
       <c r="F89" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="G89" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -10025,7 +10021,7 @@
       </c>
       <c r="AC89" s="6"/>
       <c r="AD89" s="6" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="AE89" s="6" t="s">
         <v>188</v>
@@ -10034,28 +10030,28 @@
         <v>189</v>
       </c>
       <c r="AH89" t="s">
+        <v>716</v>
+      </c>
+      <c r="AJ89" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="AK89" s="27" t="s">
+        <v>718</v>
+      </c>
+      <c r="AL89" s="27" t="s">
         <v>717</v>
       </c>
-      <c r="AJ89" s="27" t="s">
-        <v>280</v>
-      </c>
-      <c r="AK89" s="27" t="s">
+      <c r="AM89" s="27" t="s">
         <v>719</v>
       </c>
-      <c r="AL89" s="27" t="s">
-        <v>718</v>
-      </c>
-      <c r="AM89" s="27" t="s">
+      <c r="AO89" t="s">
         <v>720</v>
       </c>
-      <c r="AO89" t="s">
-        <v>721</v>
-      </c>
       <c r="AP89" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="BA89" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="90" spans="1:58" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -10072,10 +10068,10 @@
         <v>190</v>
       </c>
       <c r="F90" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G90" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -10093,7 +10089,7 @@
         <v>192</v>
       </c>
       <c r="M90" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O90" t="s">
         <v>35</v>
@@ -10105,10 +10101,10 @@
         <v>1</v>
       </c>
       <c r="R90" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="S90" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="T90">
         <v>10</v>
@@ -10135,41 +10131,41 @@
         <v>2024</v>
       </c>
       <c r="AD90" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AE90" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AF90" s="15" t="s">
         <v>193</v>
       </c>
       <c r="AI90" s="27" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AJ90" s="27" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AK90" s="27" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AL90" s="27" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AM90" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AN90" s="27"/>
       <c r="AO90" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AP90" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AQ90" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="BA90" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="BF90" s="2"/>
     </row>
@@ -10186,29 +10182,24 @@
       <c r="D91" t="s">
         <v>194</v>
       </c>
+      <c r="H91" t="s">
+        <v>661</v>
+      </c>
       <c r="I91">
         <v>1</v>
       </c>
       <c r="X91" s="4"/>
       <c r="Z91" s="4"/>
-      <c r="AF91" s="15" t="s">
-        <v>197</v>
-      </c>
+      <c r="AF91" s="15"/>
       <c r="AI91" s="27"/>
       <c r="AJ91" s="27"/>
       <c r="AK91" s="27"/>
       <c r="AL91" s="27"/>
       <c r="AN91" s="27"/>
-      <c r="AX91" t="s">
-        <v>574</v>
-      </c>
-      <c r="BA91" t="s">
-        <v>617</v>
-      </c>
     </row>
     <row r="92" spans="1:58" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B92" s="4">
         <v>1</v>
@@ -10217,19 +10208,19 @@
         <v>194</v>
       </c>
       <c r="D92" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E92" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F92" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G92" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H92" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I92">
         <v>1</v>
@@ -10241,7 +10232,7 @@
         <v>195</v>
       </c>
       <c r="L92" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M92" t="s">
         <v>39</v>
@@ -10267,51 +10258,51 @@
         <v>2024</v>
       </c>
       <c r="AB92" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="AE92" t="s">
         <v>196</v>
       </c>
       <c r="AF92" s="15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG92" s="2"/>
       <c r="AH92" s="2"/>
       <c r="AI92" s="27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AJ92" s="27" t="s">
+        <v>609</v>
+      </c>
+      <c r="AK92" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="AL92" s="27" t="s">
         <v>610</v>
       </c>
-      <c r="AK92" s="27" t="s">
-        <v>285</v>
-      </c>
-      <c r="AL92" s="27" t="s">
-        <v>611</v>
-      </c>
       <c r="AM92" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AN92" s="27"/>
       <c r="AO92" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AP92" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AQ92" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AX92" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="BA92" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="93" spans="1:58" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B93" s="4">
         <v>1</v>
@@ -10320,19 +10311,19 @@
         <v>194</v>
       </c>
       <c r="D93" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E93" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F93" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G93" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H93" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I93">
         <v>1</v>
@@ -10344,7 +10335,7 @@
         <v>195</v>
       </c>
       <c r="L93" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M93" t="s">
         <v>39</v>
@@ -10370,51 +10361,51 @@
         <v>2024</v>
       </c>
       <c r="AB93" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="AE93" t="s">
         <v>196</v>
       </c>
       <c r="AF93" s="15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG93" s="2"/>
       <c r="AH93" s="2"/>
       <c r="AI93" s="27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AJ93" s="27" t="s">
+        <v>609</v>
+      </c>
+      <c r="AK93" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="AL93" s="27" t="s">
         <v>610</v>
       </c>
-      <c r="AK93" s="27" t="s">
-        <v>285</v>
-      </c>
-      <c r="AL93" s="27" t="s">
-        <v>611</v>
-      </c>
       <c r="AM93" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AN93" s="27"/>
       <c r="AO93" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AP93" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AQ93" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AX93" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="BA93" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="94" spans="1:58" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B94" s="4">
         <v>1</v>
@@ -10423,19 +10414,19 @@
         <v>194</v>
       </c>
       <c r="D94" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E94" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F94" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G94" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H94" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I94">
         <v>1</v>
@@ -10447,7 +10438,7 @@
         <v>195</v>
       </c>
       <c r="L94" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="M94" t="s">
         <v>39</v>
@@ -10473,51 +10464,51 @@
         <v>2024</v>
       </c>
       <c r="AB94" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="AE94" t="s">
         <v>196</v>
       </c>
       <c r="AF94" s="15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG94" s="2"/>
       <c r="AH94" s="2"/>
       <c r="AI94" s="27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AJ94" s="27" t="s">
+        <v>609</v>
+      </c>
+      <c r="AK94" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="AL94" s="27" t="s">
         <v>610</v>
       </c>
-      <c r="AK94" s="27" t="s">
-        <v>285</v>
-      </c>
-      <c r="AL94" s="27" t="s">
-        <v>611</v>
-      </c>
       <c r="AM94" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AN94" s="27"/>
       <c r="AO94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AP94" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AQ94" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AX94" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="BA94" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="95" spans="1:58" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B95" s="4">
         <v>1</v>
@@ -10526,19 +10517,19 @@
         <v>194</v>
       </c>
       <c r="D95" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E95" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F95" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G95" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H95" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I95">
         <v>1</v>
@@ -10550,7 +10541,7 @@
         <v>195</v>
       </c>
       <c r="L95" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M95" t="s">
         <v>39</v>
@@ -10576,51 +10567,51 @@
         <v>2024</v>
       </c>
       <c r="AB95" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="AE95" t="s">
         <v>196</v>
       </c>
       <c r="AF95" s="15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG95" s="2"/>
       <c r="AH95" s="2"/>
       <c r="AI95" s="27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AJ95" s="27" t="s">
+        <v>609</v>
+      </c>
+      <c r="AK95" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="AL95" s="27" t="s">
         <v>610</v>
       </c>
-      <c r="AK95" s="27" t="s">
-        <v>285</v>
-      </c>
-      <c r="AL95" s="27" t="s">
-        <v>611</v>
-      </c>
       <c r="AM95" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AN95" s="27"/>
       <c r="AO95" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AP95" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AQ95" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AX95" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="BA95" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="96" spans="1:58" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B96" s="4">
         <v>1</v>
@@ -10629,19 +10620,19 @@
         <v>194</v>
       </c>
       <c r="D96" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E96" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F96" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G96" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H96" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I96">
         <v>1</v>
@@ -10653,7 +10644,7 @@
         <v>195</v>
       </c>
       <c r="L96" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M96" t="s">
         <v>39</v>
@@ -10679,51 +10670,51 @@
         <v>2024</v>
       </c>
       <c r="AB96" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="AE96" t="s">
         <v>196</v>
       </c>
       <c r="AF96" s="15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG96" s="2"/>
       <c r="AH96" s="2"/>
       <c r="AI96" s="27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AJ96" s="27" t="s">
+        <v>609</v>
+      </c>
+      <c r="AK96" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="AL96" s="27" t="s">
         <v>610</v>
       </c>
-      <c r="AK96" s="27" t="s">
-        <v>285</v>
-      </c>
-      <c r="AL96" s="27" t="s">
-        <v>611</v>
-      </c>
       <c r="AM96" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AN96" s="27"/>
       <c r="AO96" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AP96" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AQ96" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AX96" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="BA96" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="97" spans="1:53" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B97" s="4">
         <v>1</v>
@@ -10732,19 +10723,19 @@
         <v>194</v>
       </c>
       <c r="D97" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E97" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F97" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G97" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H97" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I97">
         <v>1</v>
@@ -10756,7 +10747,7 @@
         <v>195</v>
       </c>
       <c r="L97" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M97" t="s">
         <v>39</v>
@@ -10782,50 +10773,50 @@
         <v>2024</v>
       </c>
       <c r="AB97" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="AE97" t="s">
         <v>196</v>
       </c>
       <c r="AF97" s="15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG97" s="2"/>
       <c r="AH97" s="2"/>
       <c r="AI97" s="27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AJ97" s="27" t="s">
+        <v>609</v>
+      </c>
+      <c r="AK97" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="AL97" s="27" t="s">
         <v>610</v>
       </c>
-      <c r="AK97" s="27" t="s">
-        <v>285</v>
-      </c>
-      <c r="AL97" s="27" t="s">
+      <c r="AM97" t="s">
+        <v>286</v>
+      </c>
+      <c r="AO97" t="s">
+        <v>280</v>
+      </c>
+      <c r="AP97" t="s">
         <v>611</v>
       </c>
-      <c r="AM97" t="s">
-        <v>287</v>
-      </c>
-      <c r="AO97" t="s">
-        <v>281</v>
-      </c>
-      <c r="AP97" t="s">
-        <v>612</v>
-      </c>
       <c r="AQ97" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AX97" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="BA97" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="98" spans="1:53" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B98" s="4">
         <v>1</v>
@@ -10834,19 +10825,19 @@
         <v>194</v>
       </c>
       <c r="D98" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E98" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F98" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G98" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H98" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I98">
         <v>1</v>
@@ -10858,7 +10849,7 @@
         <v>195</v>
       </c>
       <c r="L98" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M98" t="s">
         <v>39</v>
@@ -10884,51 +10875,51 @@
         <v>2024</v>
       </c>
       <c r="AB98" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="AE98" t="s">
         <v>196</v>
       </c>
       <c r="AF98" s="15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG98" s="2"/>
       <c r="AH98" s="2"/>
       <c r="AI98" s="27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AJ98" s="27" t="s">
+        <v>609</v>
+      </c>
+      <c r="AK98" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="AL98" s="27" t="s">
         <v>610</v>
       </c>
-      <c r="AK98" s="27" t="s">
-        <v>285</v>
-      </c>
-      <c r="AL98" s="27" t="s">
-        <v>611</v>
-      </c>
       <c r="AM98" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AN98" s="27"/>
       <c r="AO98" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AP98" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AQ98" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AX98" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="BA98" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="99" spans="1:53" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B99" s="4">
         <v>1</v>
@@ -10937,19 +10928,19 @@
         <v>194</v>
       </c>
       <c r="D99" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E99" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F99" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G99" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H99" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I99">
         <v>1</v>
@@ -10961,7 +10952,7 @@
         <v>195</v>
       </c>
       <c r="L99" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M99" t="s">
         <v>39</v>
@@ -10987,51 +10978,51 @@
         <v>2024</v>
       </c>
       <c r="AB99" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="AE99" t="s">
         <v>196</v>
       </c>
       <c r="AF99" s="15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG99" s="2"/>
       <c r="AH99" s="2"/>
       <c r="AI99" s="27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AJ99" s="27" t="s">
+        <v>609</v>
+      </c>
+      <c r="AK99" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="AL99" s="27" t="s">
         <v>610</v>
       </c>
-      <c r="AK99" s="27" t="s">
-        <v>285</v>
-      </c>
-      <c r="AL99" s="27" t="s">
-        <v>611</v>
-      </c>
       <c r="AM99" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AN99" s="27"/>
       <c r="AO99" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AP99" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AQ99" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AX99" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="BA99" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="100" spans="1:53" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B100" s="4">
         <v>1</v>
@@ -11040,19 +11031,19 @@
         <v>194</v>
       </c>
       <c r="D100" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E100" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F100" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="G100" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H100" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I100">
         <v>1</v>
@@ -11064,7 +11055,7 @@
         <v>195</v>
       </c>
       <c r="L100" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M100" t="s">
         <v>39</v>
@@ -11087,40 +11078,40 @@
         <v>2021</v>
       </c>
       <c r="AE100" t="s">
+        <v>216</v>
+      </c>
+      <c r="AF100" s="15" t="s">
         <v>217</v>
-      </c>
-      <c r="AF100" s="15" t="s">
-        <v>218</v>
       </c>
       <c r="AG100" s="2"/>
       <c r="AH100" s="2"/>
       <c r="AI100" s="27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AJ100" s="27" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AK100" s="27" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AL100" s="27"/>
       <c r="AM100" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AN100" s="27"/>
       <c r="AP100" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AX100" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="BA100" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="101" spans="1:53" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B101" s="4">
         <v>1</v>
@@ -11129,19 +11120,19 @@
         <v>194</v>
       </c>
       <c r="D101" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E101" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F101" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="G101" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H101" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I101">
         <v>1</v>
@@ -11153,7 +11144,7 @@
         <v>195</v>
       </c>
       <c r="L101" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M101" t="s">
         <v>39</v>
@@ -11176,40 +11167,40 @@
         <v>2021</v>
       </c>
       <c r="AE101" t="s">
+        <v>216</v>
+      </c>
+      <c r="AF101" s="15" t="s">
         <v>217</v>
-      </c>
-      <c r="AF101" s="15" t="s">
-        <v>218</v>
       </c>
       <c r="AG101" s="2"/>
       <c r="AH101" s="2"/>
       <c r="AI101" s="27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AJ101" s="27" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AK101" s="27" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AL101" s="27"/>
       <c r="AM101" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AN101" s="27"/>
       <c r="AP101" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AX101" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="BA101" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="102" spans="1:53" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B102" s="4">
         <v>1</v>
@@ -11218,19 +11209,19 @@
         <v>194</v>
       </c>
       <c r="D102" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E102" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F102" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="G102" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H102" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I102">
         <v>1</v>
@@ -11242,7 +11233,7 @@
         <v>195</v>
       </c>
       <c r="L102" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M102" t="s">
         <v>39</v>
@@ -11263,38 +11254,38 @@
         <v>2021</v>
       </c>
       <c r="AE102" t="s">
+        <v>216</v>
+      </c>
+      <c r="AF102" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="AF102" s="15" t="s">
-        <v>218</v>
-      </c>
       <c r="AI102" s="27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AJ102" s="27" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AK102" s="27" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AL102" s="27"/>
       <c r="AM102" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AN102" s="27"/>
       <c r="AP102" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AX102" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="BA102" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="103" spans="1:53" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B103" s="4">
         <v>1</v>
@@ -11303,19 +11294,19 @@
         <v>194</v>
       </c>
       <c r="D103" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E103" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F103" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="G103" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H103" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I103">
         <v>1</v>
@@ -11327,7 +11318,7 @@
         <v>195</v>
       </c>
       <c r="L103" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M103" t="s">
         <v>39</v>
@@ -11348,47 +11339,47 @@
         <v>2021</v>
       </c>
       <c r="AE103" t="s">
+        <v>216</v>
+      </c>
+      <c r="AF103" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="AF103" s="15" t="s">
-        <v>218</v>
-      </c>
       <c r="AI103" s="27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AJ103" s="27" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AK103" s="27" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AL103" s="27"/>
       <c r="AM103" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AN103" s="27"/>
       <c r="AP103" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AX103" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="BA103" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="104" spans="1:53" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B104" s="4">
         <v>0</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="M104"/>
       <c r="V104" t="str">
@@ -11409,25 +11400,25 @@
     </row>
     <row r="105" spans="1:53" s="4" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B105" s="4">
         <v>0</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J105" s="4" t="s">
         <v>25</v>
       </c>
       <c r="K105" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="L105" s="4" t="s">
         <v>226</v>
-      </c>
-      <c r="L105" s="4" t="s">
-        <v>227</v>
       </c>
       <c r="M105" s="4" t="s">
         <v>39</v>
@@ -11451,27 +11442,27 @@
         <v>geen data</v>
       </c>
       <c r="AE105" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="AF105" s="18" t="s">
         <v>228</v>
-      </c>
-      <c r="AF105" s="18" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="106" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B106" s="4">
         <v>0</v>
       </c>
       <c r="C106" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D106" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F106" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -11483,10 +11474,10 @@
         <v>25</v>
       </c>
       <c r="K106" t="s">
+        <v>230</v>
+      </c>
+      <c r="L106" t="s">
         <v>231</v>
-      </c>
-      <c r="L106" t="s">
-        <v>232</v>
       </c>
       <c r="M106" t="s">
         <v>26</v>
@@ -11519,71 +11510,71 @@
         <v>2011</v>
       </c>
       <c r="AD106" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="AE106" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="AF106" t="s">
         <v>233</v>
-      </c>
-      <c r="AF106" t="s">
-        <v>234</v>
       </c>
       <c r="AG106" s="27">
         <v>1</v>
       </c>
       <c r="AH106" s="27"/>
       <c r="AI106" s="27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AJ106" s="27" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AK106" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="AL106" s="27" t="s">
         <v>285</v>
       </c>
-      <c r="AL106" s="27" t="s">
+      <c r="AM106" t="s">
         <v>286</v>
-      </c>
-      <c r="AM106" t="s">
-        <v>287</v>
       </c>
       <c r="AN106" s="27"/>
       <c r="AO106" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AP106" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AQ106" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AU106" t="s">
+        <v>597</v>
+      </c>
+      <c r="AV106" t="s">
+        <v>295</v>
+      </c>
+      <c r="AX106" t="s">
+        <v>573</v>
+      </c>
+      <c r="BA106" t="s">
         <v>598</v>
-      </c>
-      <c r="AV106" t="s">
-        <v>296</v>
-      </c>
-      <c r="AX106" t="s">
-        <v>574</v>
-      </c>
-      <c r="BA106" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="107" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B107" s="4">
         <v>0</v>
       </c>
       <c r="C107" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D107" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F107" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -11631,48 +11622,48 @@
         <v>2015</v>
       </c>
       <c r="AE107" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="AF107" t="s">
         <v>236</v>
       </c>
-      <c r="AF107" t="s">
-        <v>237</v>
-      </c>
       <c r="AG107">
         <v>1</v>
       </c>
       <c r="AJ107" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AK107" t="s">
+        <v>284</v>
+      </c>
+      <c r="AL107" t="s">
         <v>285</v>
       </c>
-      <c r="AL107" t="s">
+      <c r="AM107" t="s">
         <v>286</v>
       </c>
-      <c r="AM107" t="s">
-        <v>287</v>
-      </c>
       <c r="AO107" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AQ107" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="108" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B108" s="4">
         <v>0</v>
       </c>
       <c r="C108" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D108" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F108" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -11720,57 +11711,57 @@
         <v>2025</v>
       </c>
       <c r="AD108" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AE108" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AF108" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AG108">
         <v>1</v>
       </c>
       <c r="AJ108" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AK108" t="s">
+        <v>284</v>
+      </c>
+      <c r="AL108" t="s">
         <v>285</v>
       </c>
-      <c r="AL108" t="s">
+      <c r="AM108" t="s">
         <v>286</v>
       </c>
-      <c r="AM108" t="s">
-        <v>287</v>
-      </c>
       <c r="AO108" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AQ108" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="109" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B109" s="4">
         <v>0</v>
       </c>
       <c r="C109" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D109" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="F109" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="G109" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -11782,10 +11773,10 @@
         <v>3</v>
       </c>
       <c r="K109" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L109" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M109" t="s">
         <v>26</v>
@@ -11821,51 +11812,51 @@
         <v>2015</v>
       </c>
       <c r="AD109" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AE109" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="AF109" t="s">
         <v>240</v>
       </c>
-      <c r="AF109" t="s">
-        <v>241</v>
-      </c>
       <c r="AG109">
         <v>1</v>
       </c>
       <c r="AH109" t="s">
+        <v>599</v>
+      </c>
+      <c r="AP109" t="s">
+        <v>594</v>
+      </c>
+      <c r="AS109" t="s">
         <v>600</v>
       </c>
-      <c r="AP109" t="s">
-        <v>595</v>
-      </c>
-      <c r="AS109" t="s">
+      <c r="BA109" t="s">
         <v>601</v>
-      </c>
-      <c r="BA109" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="110" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B110" s="4">
         <v>0</v>
       </c>
       <c r="C110" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D110" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="F110" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="G110" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -11877,10 +11868,10 @@
         <v>3</v>
       </c>
       <c r="K110" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L110" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M110" t="s">
         <v>26</v>
@@ -11916,51 +11907,51 @@
         <v>2022</v>
       </c>
       <c r="AD110" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="AE110" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="AF110" t="s">
         <v>240</v>
       </c>
-      <c r="AF110" t="s">
-        <v>241</v>
-      </c>
       <c r="AG110">
         <v>1</v>
       </c>
       <c r="AH110" t="s">
+        <v>599</v>
+      </c>
+      <c r="AP110" t="s">
+        <v>594</v>
+      </c>
+      <c r="AS110" t="s">
         <v>600</v>
       </c>
-      <c r="AP110" t="s">
-        <v>595</v>
-      </c>
-      <c r="AS110" t="s">
+      <c r="BA110" t="s">
         <v>601</v>
-      </c>
-      <c r="BA110" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="111" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B111" s="4">
         <v>0</v>
       </c>
       <c r="C111" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D111" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="F111" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="G111" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -11972,10 +11963,10 @@
         <v>3</v>
       </c>
       <c r="K111" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L111" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M111" t="s">
         <v>26</v>
@@ -12011,48 +12002,48 @@
         <v>2025</v>
       </c>
       <c r="AD111" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="AE111" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="AF111" t="s">
         <v>240</v>
       </c>
-      <c r="AF111" t="s">
-        <v>241</v>
-      </c>
       <c r="AG111">
         <v>1</v>
       </c>
       <c r="AH111" t="s">
+        <v>599</v>
+      </c>
+      <c r="AP111" t="s">
+        <v>594</v>
+      </c>
+      <c r="AS111" t="s">
         <v>600</v>
       </c>
-      <c r="AP111" t="s">
-        <v>595</v>
-      </c>
-      <c r="AS111" t="s">
+      <c r="BA111" t="s">
         <v>601</v>
-      </c>
-      <c r="BA111" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="112" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B112" s="4">
         <v>1</v>
       </c>
       <c r="C112" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D112" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F112" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H112" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I112">
         <v>1</v>
@@ -12085,36 +12076,36 @@
         <v>2008</v>
       </c>
       <c r="AE112" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="AF112" t="s">
         <v>243</v>
-      </c>
-      <c r="AF112" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="113" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C113" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D113" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E113" t="s">
+        <v>688</v>
+      </c>
+      <c r="F113" t="s">
         <v>689</v>
       </c>
-      <c r="F113" t="s">
+      <c r="G113" s="6" t="s">
         <v>690</v>
       </c>
-      <c r="G113" s="6" t="s">
-        <v>691</v>
-      </c>
       <c r="H113" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I113">
         <v>1</v>
@@ -12123,7 +12114,7 @@
         <v>25</v>
       </c>
       <c r="K113" s="29" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="M113" t="s">
         <v>26</v>
@@ -12150,48 +12141,48 @@
         <v>2023</v>
       </c>
       <c r="AE113" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AI113" t="s">
+        <v>681</v>
+      </c>
+      <c r="AJ113" t="s">
         <v>682</v>
       </c>
-      <c r="AJ113" t="s">
+      <c r="AK113" t="s">
         <v>683</v>
       </c>
-      <c r="AK113" t="s">
+      <c r="AL113" t="s">
         <v>684</v>
       </c>
-      <c r="AL113" t="s">
+      <c r="AN113" t="s">
         <v>685</v>
       </c>
-      <c r="AN113" t="s">
+      <c r="AO113" t="s">
         <v>686</v>
-      </c>
-      <c r="AO113" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="114" spans="1:55" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B114" s="4">
         <v>1</v>
       </c>
       <c r="C114" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D114" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F114" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G114" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H114" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I114">
         <v>1</v>
@@ -12230,39 +12221,39 @@
         <v>2023</v>
       </c>
       <c r="AD114" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="AE114" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AF114" s="13" t="s">
         <v>37</v>
       </c>
       <c r="AI114" s="27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="115" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B115" s="4">
         <v>0</v>
       </c>
       <c r="C115" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D115" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E115" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F115" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="G115" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -12274,16 +12265,16 @@
         <v>3</v>
       </c>
       <c r="K115" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L115" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M115" t="s">
         <v>26</v>
       </c>
       <c r="N115" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="O115" t="s">
         <v>35</v>
@@ -12319,48 +12310,48 @@
         <v>2019</v>
       </c>
       <c r="AD115" s="6" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="AF115" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AG115">
         <v>1</v>
       </c>
       <c r="AI115" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AJ115" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AQ115" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AX115" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="116" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B116" s="4">
         <v>0</v>
       </c>
       <c r="C116" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D116" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E116" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="F116" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="G116" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -12372,16 +12363,16 @@
         <v>3</v>
       </c>
       <c r="K116" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L116" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M116" t="s">
         <v>26</v>
       </c>
       <c r="N116" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="O116" t="s">
         <v>35</v>
@@ -12414,57 +12405,57 @@
         <v>2018</v>
       </c>
       <c r="AB116" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="AD116" s="6" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="AF116" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AG116">
         <v>1</v>
       </c>
       <c r="AI116" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AJ116" t="s">
+        <v>602</v>
+      </c>
+      <c r="AK116" t="s">
+        <v>284</v>
+      </c>
+      <c r="AO116" t="s">
+        <v>280</v>
+      </c>
+      <c r="AP116" t="s">
+        <v>594</v>
+      </c>
+      <c r="AQ116" t="s">
+        <v>274</v>
+      </c>
+      <c r="BA116" t="s">
         <v>603</v>
-      </c>
-      <c r="AK116" t="s">
-        <v>285</v>
-      </c>
-      <c r="AO116" t="s">
-        <v>281</v>
-      </c>
-      <c r="AP116" t="s">
-        <v>595</v>
-      </c>
-      <c r="AQ116" t="s">
-        <v>275</v>
-      </c>
-      <c r="BA116" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="117" spans="1:55" ht="75" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B117" s="4">
         <v>0</v>
       </c>
       <c r="C117" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D117" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E117" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="F117" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -12476,10 +12467,10 @@
         <v>3</v>
       </c>
       <c r="K117" t="s">
+        <v>252</v>
+      </c>
+      <c r="L117" t="s">
         <v>253</v>
-      </c>
-      <c r="L117" t="s">
-        <v>254</v>
       </c>
       <c r="M117" t="s">
         <v>26</v>
@@ -12515,63 +12506,63 @@
         <v>2024</v>
       </c>
       <c r="AE117" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="AF117" t="s">
         <v>255</v>
       </c>
-      <c r="AF117" t="s">
-        <v>256</v>
-      </c>
       <c r="AG117">
         <v>1</v>
       </c>
       <c r="AI117" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AJ117" t="s">
+        <v>279</v>
+      </c>
+      <c r="AK117" s="15" t="s">
+        <v>699</v>
+      </c>
+      <c r="AO117" t="s">
         <v>280</v>
       </c>
-      <c r="AK117" s="15" t="s">
-        <v>700</v>
-      </c>
-      <c r="AO117" t="s">
-        <v>281</v>
-      </c>
       <c r="AQ117" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AU117" s="29" t="s">
+        <v>701</v>
+      </c>
+      <c r="AV117" s="15" t="s">
         <v>702</v>
       </c>
-      <c r="AV117" s="15" t="s">
-        <v>703</v>
-      </c>
       <c r="AX117" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="BA117" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="118" spans="1:55" ht="75" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B118" s="4">
         <v>0</v>
       </c>
       <c r="C118" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D118" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E118" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="F118" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="G118" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -12583,10 +12574,10 @@
         <v>3</v>
       </c>
       <c r="K118" t="s">
+        <v>252</v>
+      </c>
+      <c r="L118" t="s">
         <v>253</v>
-      </c>
-      <c r="L118" t="s">
-        <v>254</v>
       </c>
       <c r="M118" t="s">
         <v>26</v>
@@ -12622,57 +12613,57 @@
         <v>2024</v>
       </c>
       <c r="AB118" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="AE118" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="AF118" t="s">
         <v>255</v>
       </c>
-      <c r="AF118" t="s">
-        <v>256</v>
-      </c>
       <c r="AG118">
         <v>1</v>
       </c>
       <c r="AI118" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AJ118" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AK118" s="15" t="s">
+        <v>699</v>
+      </c>
+      <c r="AO118" t="s">
         <v>700</v>
       </c>
-      <c r="AO118" t="s">
+      <c r="AQ118" t="s">
+        <v>274</v>
+      </c>
+      <c r="AU118" s="29" t="s">
         <v>701</v>
       </c>
-      <c r="AQ118" t="s">
-        <v>275</v>
-      </c>
-      <c r="AU118" s="29" t="s">
+      <c r="AV118" s="15" t="s">
         <v>702</v>
       </c>
-      <c r="AV118" s="15" t="s">
+      <c r="AX118" t="s">
         <v>703</v>
       </c>
-      <c r="AX118" t="s">
+      <c r="BA118" t="s">
         <v>704</v>
-      </c>
-      <c r="BA118" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="119" spans="1:55" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B119" s="4">
         <v>0</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="V119" t="str">
         <f>IF(NOT(ISBLANK(T119)), IF(T119&gt;=AVERAGE($T$2:$T$124), 1, 0), IF(NOT(ISBLANK(U119)), IF(U119&gt;=AVERAGE($U$2:$U$124), 1, 0), "geen data"))</f>
@@ -12713,16 +12704,16 @@
     </row>
     <row r="120" spans="1:55" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B120" s="4">
         <v>0</v>
       </c>
       <c r="C120" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D120" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J120" t="s">
         <v>25</v>
@@ -12743,33 +12734,33 @@
         <v>geen data</v>
       </c>
       <c r="AF120" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="121" spans="1:55" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B121" s="4">
         <v>1</v>
       </c>
       <c r="C121" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D121" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E121" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="F121" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G121" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H121" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I121">
         <v>1</v>
@@ -12778,10 +12769,10 @@
         <v>25</v>
       </c>
       <c r="K121" t="s">
+        <v>260</v>
+      </c>
+      <c r="L121" t="s">
         <v>261</v>
-      </c>
-      <c r="L121" t="s">
-        <v>262</v>
       </c>
       <c r="M121" t="s">
         <v>26</v>
@@ -12817,61 +12808,61 @@
         <v>2023</v>
       </c>
       <c r="AE121" t="s">
+        <v>262</v>
+      </c>
+      <c r="AF121" s="15" t="s">
         <v>263</v>
-      </c>
-      <c r="AF121" s="15" t="s">
-        <v>264</v>
       </c>
       <c r="AG121" s="27">
         <v>1</v>
       </c>
       <c r="AH121" s="27"/>
       <c r="AI121" s="27" t="s">
+        <v>604</v>
+      </c>
+      <c r="AJ121" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="AK121" s="27" t="s">
         <v>605</v>
       </c>
-      <c r="AJ121" s="27" t="s">
-        <v>280</v>
-      </c>
-      <c r="AK121" s="27" t="s">
+      <c r="AL121" t="s">
         <v>606</v>
       </c>
-      <c r="AL121" t="s">
+      <c r="AM121" s="27" t="s">
         <v>607</v>
       </c>
-      <c r="AM121" s="27" t="s">
+      <c r="AO121" t="s">
+        <v>283</v>
+      </c>
+      <c r="BA121" t="s">
         <v>608</v>
-      </c>
-      <c r="AO121" t="s">
-        <v>284</v>
-      </c>
-      <c r="BA121" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="122" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B122" s="4">
         <v>1</v>
       </c>
       <c r="C122" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D122" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E122" t="s">
+        <v>655</v>
+      </c>
+      <c r="F122" t="s">
         <v>656</v>
       </c>
-      <c r="F122" t="s">
-        <v>657</v>
-      </c>
       <c r="G122" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H122" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I122">
         <v>1</v>
@@ -12880,13 +12871,13 @@
         <v>25</v>
       </c>
       <c r="K122" t="s">
+        <v>260</v>
+      </c>
+      <c r="L122" t="s">
         <v>261</v>
       </c>
-      <c r="L122" t="s">
-        <v>262</v>
-      </c>
       <c r="M122" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O122" t="s">
         <v>35</v>
@@ -12925,10 +12916,10 @@
         <v>2023</v>
       </c>
       <c r="AE122" t="s">
+        <v>265</v>
+      </c>
+      <c r="AF122" t="s">
         <v>266</v>
-      </c>
-      <c r="AF122" t="s">
-        <v>267</v>
       </c>
       <c r="AG122" s="27">
         <v>1</v>
@@ -12936,45 +12927,45 @@
       <c r="AH122" s="27"/>
       <c r="AI122" s="27"/>
       <c r="AJ122" s="27" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AK122" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="AL122" s="27" t="s">
         <v>285</v>
       </c>
-      <c r="AL122" s="27" t="s">
+      <c r="AM122" t="s">
         <v>286</v>
       </c>
-      <c r="AM122" t="s">
-        <v>287</v>
-      </c>
       <c r="AO122" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AP122" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="123" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B123" s="4">
         <v>1</v>
       </c>
       <c r="C123" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D123" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E123" t="s">
+        <v>657</v>
+      </c>
+      <c r="F123" t="s">
         <v>658</v>
       </c>
-      <c r="F123" t="s">
-        <v>659</v>
-      </c>
       <c r="H123" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I123">
         <v>1</v>
@@ -12983,19 +12974,19 @@
         <v>25</v>
       </c>
       <c r="K123" t="s">
+        <v>260</v>
+      </c>
+      <c r="L123" t="s">
         <v>261</v>
-      </c>
-      <c r="L123" t="s">
-        <v>262</v>
       </c>
       <c r="M123" t="s">
         <v>39</v>
       </c>
       <c r="N123" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="O123" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="V123" t="str">
         <f>IF(NOT(ISBLANK(T123)), IF(T123&gt;=AVERAGE($T$2:$T$124), 1, 0), IF(NOT(ISBLANK(U123)), IF(U123&gt;=AVERAGE($U$2:$U$124), 1, 0), "geen data"))</f>
@@ -13016,48 +13007,48 @@
         <v>2024</v>
       </c>
       <c r="AE123" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="AF123" t="s">
         <v>270</v>
       </c>
-      <c r="AF123" t="s">
-        <v>271</v>
-      </c>
       <c r="AG123">
         <v>1</v>
       </c>
       <c r="AJ123" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AK123" t="s">
+        <v>605</v>
+      </c>
+      <c r="AL123" t="s">
         <v>606</v>
       </c>
-      <c r="AL123" t="s">
+      <c r="AM123" t="s">
         <v>607</v>
       </c>
-      <c r="AM123" t="s">
-        <v>608</v>
-      </c>
       <c r="AO123" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="124" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B124" s="4">
         <v>1</v>
       </c>
       <c r="C124" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D124" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F124" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H124" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I124">
         <v>1</v>
@@ -13066,10 +13057,10 @@
         <v>25</v>
       </c>
       <c r="K124" t="s">
+        <v>260</v>
+      </c>
+      <c r="L124" t="s">
         <v>261</v>
-      </c>
-      <c r="L124" t="s">
-        <v>262</v>
       </c>
       <c r="M124" t="s">
         <v>39</v>
@@ -13120,36 +13111,36 @@
         <v>2023</v>
       </c>
       <c r="AD124" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="AE124" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="AF124" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="125" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B125" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C125" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D125" t="s">
+        <v>381</v>
+      </c>
+      <c r="F125" t="s">
+        <v>380</v>
+      </c>
+      <c r="G125" t="s">
         <v>382</v>
       </c>
-      <c r="F125" t="s">
-        <v>381</v>
-      </c>
-      <c r="G125" t="s">
-        <v>383</v>
-      </c>
       <c r="H125" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="I125">
         <v>1</v>
@@ -13158,19 +13149,19 @@
         <v>25</v>
       </c>
       <c r="K125" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="M125" t="s">
         <v>39</v>
       </c>
       <c r="N125" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O125" t="s">
         <v>35</v>
       </c>
       <c r="U125" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AA125">
         <v>2022</v>
@@ -13179,16 +13170,16 @@
         <v>2022</v>
       </c>
       <c r="AC125" s="24" t="s">
+        <v>385</v>
+      </c>
+      <c r="AD125" t="s">
         <v>386</v>
       </c>
-      <c r="AD125" t="s">
+      <c r="AE125" t="s">
+        <v>386</v>
+      </c>
+      <c r="AF125" t="s">
         <v>387</v>
-      </c>
-      <c r="AE125" t="s">
-        <v>387</v>
-      </c>
-      <c r="AF125" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -13196,22 +13187,22 @@
         <v>88</v>
       </c>
       <c r="B126" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C126" t="s">
         <v>88</v>
       </c>
       <c r="D126" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F126" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G126" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H126" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="I126">
         <v>1</v>
@@ -13223,16 +13214,16 @@
         <v>26</v>
       </c>
       <c r="N126" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O126" t="s">
         <v>35</v>
       </c>
       <c r="T126" t="s">
+        <v>390</v>
+      </c>
+      <c r="U126" t="s">
         <v>391</v>
-      </c>
-      <c r="U126" t="s">
-        <v>392</v>
       </c>
       <c r="AA126">
         <v>2013</v>
@@ -13241,16 +13232,16 @@
         <v>2013</v>
       </c>
       <c r="AC126" s="24" t="s">
+        <v>392</v>
+      </c>
+      <c r="AD126" t="s">
         <v>393</v>
       </c>
-      <c r="AD126" t="s">
+      <c r="AE126" t="s">
+        <v>393</v>
+      </c>
+      <c r="AF126" t="s">
         <v>394</v>
-      </c>
-      <c r="AE126" t="s">
-        <v>394</v>
-      </c>
-      <c r="AF126" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="127" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -13258,22 +13249,22 @@
         <v>172</v>
       </c>
       <c r="B127" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C127" t="s">
         <v>172</v>
       </c>
       <c r="D127" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F127" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G127" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H127" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="I127">
         <v>1</v>
@@ -13282,22 +13273,22 @@
         <v>25</v>
       </c>
       <c r="K127" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="M127" t="s">
         <v>26</v>
       </c>
       <c r="N127" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O127" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="T127" t="s">
+        <v>398</v>
+      </c>
+      <c r="U127" t="s">
         <v>399</v>
-      </c>
-      <c r="U127" t="s">
-        <v>400</v>
       </c>
       <c r="AA127">
         <v>2021</v>
@@ -13306,16 +13297,16 @@
         <v>2021</v>
       </c>
       <c r="AC127" s="25" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AD127" t="s">
+        <v>400</v>
+      </c>
+      <c r="AE127" t="s">
+        <v>400</v>
+      </c>
+      <c r="AF127" t="s">
         <v>401</v>
-      </c>
-      <c r="AE127" t="s">
-        <v>401</v>
-      </c>
-      <c r="AF127" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="128" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -13323,22 +13314,22 @@
         <v>88</v>
       </c>
       <c r="B128" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C128" t="s">
         <v>88</v>
       </c>
       <c r="D128" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F128" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G128" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H128" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="I128">
         <v>1</v>
@@ -13347,22 +13338,22 @@
         <v>25</v>
       </c>
       <c r="K128" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M128" t="s">
         <v>26</v>
       </c>
       <c r="N128" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O128" t="s">
         <v>35</v>
       </c>
       <c r="T128" t="s">
+        <v>405</v>
+      </c>
+      <c r="U128" t="s">
         <v>406</v>
-      </c>
-      <c r="U128" t="s">
-        <v>407</v>
       </c>
       <c r="AA128">
         <v>2021</v>
@@ -13371,39 +13362,39 @@
         <v>2021</v>
       </c>
       <c r="AC128" s="25" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AD128" t="s">
+        <v>407</v>
+      </c>
+      <c r="AE128" t="s">
+        <v>407</v>
+      </c>
+      <c r="AF128" t="s">
         <v>408</v>
-      </c>
-      <c r="AE128" t="s">
-        <v>408</v>
-      </c>
-      <c r="AF128" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="129" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>410</v>
+      </c>
+      <c r="B129" s="22" t="s">
+        <v>618</v>
+      </c>
+      <c r="C129" t="s">
+        <v>410</v>
+      </c>
+      <c r="D129" t="s">
         <v>411</v>
       </c>
-      <c r="B129" s="22" t="s">
-        <v>619</v>
-      </c>
-      <c r="C129" t="s">
-        <v>411</v>
-      </c>
-      <c r="D129" t="s">
+      <c r="F129" t="s">
+        <v>409</v>
+      </c>
+      <c r="G129" t="s">
         <v>412</v>
       </c>
-      <c r="F129" t="s">
-        <v>410</v>
-      </c>
-      <c r="G129" t="s">
-        <v>413</v>
-      </c>
       <c r="H129" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="I129">
         <v>1</v>
@@ -13412,22 +13403,22 @@
         <v>25</v>
       </c>
       <c r="K129" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M129" t="s">
         <v>26</v>
       </c>
       <c r="N129" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O129" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="T129" t="s">
+        <v>414</v>
+      </c>
+      <c r="U129" t="s">
         <v>415</v>
-      </c>
-      <c r="U129" t="s">
-        <v>416</v>
       </c>
       <c r="AA129">
         <v>2024</v>
@@ -13436,39 +13427,39 @@
         <v>2024</v>
       </c>
       <c r="AC129" s="24" t="s">
+        <v>416</v>
+      </c>
+      <c r="AD129" t="s">
         <v>417</v>
       </c>
-      <c r="AD129" t="s">
+      <c r="AE129" t="s">
+        <v>417</v>
+      </c>
+      <c r="AF129" t="s">
         <v>418</v>
-      </c>
-      <c r="AE129" t="s">
-        <v>418</v>
-      </c>
-      <c r="AF129" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="130" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B130" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C130" t="s">
         <v>135</v>
       </c>
       <c r="D130" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F130" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G130" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H130" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="I130">
         <v>1</v>
@@ -13480,16 +13471,16 @@
         <v>26</v>
       </c>
       <c r="N130" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O130" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="T130" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="U130" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AA130">
         <v>2023</v>
@@ -13498,16 +13489,16 @@
         <v>2023</v>
       </c>
       <c r="AC130" s="25" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AD130" t="s">
+        <v>423</v>
+      </c>
+      <c r="AE130" t="s">
+        <v>423</v>
+      </c>
+      <c r="AF130" t="s">
         <v>424</v>
-      </c>
-      <c r="AE130" t="s">
-        <v>424</v>
-      </c>
-      <c r="AF130" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="131" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -13515,22 +13506,22 @@
         <v>128</v>
       </c>
       <c r="B131" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C131" t="s">
         <v>128</v>
       </c>
       <c r="D131" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F131" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G131" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H131" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="I131">
         <v>1</v>
@@ -13542,16 +13533,16 @@
         <v>26</v>
       </c>
       <c r="N131" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O131" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="T131" t="s">
+        <v>427</v>
+      </c>
+      <c r="U131" t="s">
         <v>428</v>
-      </c>
-      <c r="U131" t="s">
-        <v>429</v>
       </c>
       <c r="AA131">
         <v>2021</v>
@@ -13560,16 +13551,16 @@
         <v>2021</v>
       </c>
       <c r="AC131" s="24" t="s">
+        <v>429</v>
+      </c>
+      <c r="AD131" t="s">
         <v>430</v>
       </c>
-      <c r="AD131" t="s">
+      <c r="AE131" t="s">
+        <v>430</v>
+      </c>
+      <c r="AF131" t="s">
         <v>431</v>
-      </c>
-      <c r="AE131" t="s">
-        <v>431</v>
-      </c>
-      <c r="AF131" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="132" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -13577,22 +13568,22 @@
         <v>128</v>
       </c>
       <c r="B132" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C132" t="s">
         <v>128</v>
       </c>
       <c r="D132" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F132" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G132" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H132" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="I132">
         <v>1</v>
@@ -13601,22 +13592,22 @@
         <v>25</v>
       </c>
       <c r="K132" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="M132" t="s">
         <v>26</v>
       </c>
       <c r="N132" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O132" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="T132" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="U132" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AA132">
         <v>2022</v>
@@ -13625,16 +13616,16 @@
         <v>2022</v>
       </c>
       <c r="AC132" s="25" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AD132" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AE132" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AF132" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="133" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -13642,22 +13633,22 @@
         <v>83</v>
       </c>
       <c r="B133" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C133" t="s">
         <v>83</v>
       </c>
       <c r="D133" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F133" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G133" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H133" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="I133">
         <v>1</v>
@@ -13666,22 +13657,22 @@
         <v>25</v>
       </c>
       <c r="K133" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="M133" t="s">
         <v>26</v>
       </c>
       <c r="N133" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O133" t="s">
         <v>35</v>
       </c>
       <c r="T133" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="U133" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AA133">
         <v>2021</v>
@@ -13690,16 +13681,16 @@
         <v>2021</v>
       </c>
       <c r="AC133" s="25" t="s">
+        <v>440</v>
+      </c>
+      <c r="AD133" t="s">
         <v>441</v>
       </c>
-      <c r="AD133" t="s">
+      <c r="AE133" t="s">
+        <v>441</v>
+      </c>
+      <c r="AF133" t="s">
         <v>442</v>
-      </c>
-      <c r="AE133" t="s">
-        <v>442</v>
-      </c>
-      <c r="AF133" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="134" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -13707,22 +13698,22 @@
         <v>83</v>
       </c>
       <c r="B134" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C134" t="s">
         <v>83</v>
       </c>
       <c r="D134" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F134" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G134" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H134" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="I134">
         <v>1</v>
@@ -13731,22 +13722,22 @@
         <v>25</v>
       </c>
       <c r="K134" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="M134" t="s">
         <v>39</v>
       </c>
       <c r="N134" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O134" t="s">
         <v>35</v>
       </c>
       <c r="T134" t="s">
+        <v>445</v>
+      </c>
+      <c r="U134" t="s">
         <v>446</v>
-      </c>
-      <c r="U134" t="s">
-        <v>447</v>
       </c>
       <c r="AA134">
         <v>2023</v>
@@ -13755,16 +13746,16 @@
         <v>2023</v>
       </c>
       <c r="AC134" s="24" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AD134" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AE134" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AF134" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="135" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -13772,22 +13763,22 @@
         <v>83</v>
       </c>
       <c r="B135" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C135" t="s">
         <v>83</v>
       </c>
       <c r="D135" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F135" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G135" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H135" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="I135">
         <v>1</v>
@@ -13796,22 +13787,22 @@
         <v>25</v>
       </c>
       <c r="K135" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="M135" t="s">
         <v>39</v>
       </c>
       <c r="N135" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O135" t="s">
         <v>35</v>
       </c>
       <c r="T135" t="s">
+        <v>450</v>
+      </c>
+      <c r="U135" t="s">
         <v>451</v>
-      </c>
-      <c r="U135" t="s">
-        <v>452</v>
       </c>
       <c r="AA135">
         <v>2023</v>
@@ -13820,16 +13811,16 @@
         <v>2023</v>
       </c>
       <c r="AC135" s="25" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AD135" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AE135" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AF135" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="136" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -13837,22 +13828,22 @@
         <v>172</v>
       </c>
       <c r="B136" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C136" t="s">
         <v>172</v>
       </c>
       <c r="D136" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F136" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G136" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H136" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="I136">
         <v>1</v>
@@ -13861,22 +13852,22 @@
         <v>25</v>
       </c>
       <c r="K136" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="M136" t="s">
         <v>26</v>
       </c>
       <c r="N136" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O136" t="s">
+        <v>455</v>
+      </c>
+      <c r="T136" t="s">
         <v>456</v>
       </c>
-      <c r="T136" t="s">
+      <c r="U136" t="s">
         <v>457</v>
-      </c>
-      <c r="U136" t="s">
-        <v>458</v>
       </c>
       <c r="AA136">
         <v>2020</v>
@@ -13885,16 +13876,16 @@
         <v>2020</v>
       </c>
       <c r="AC136" s="24" t="s">
+        <v>458</v>
+      </c>
+      <c r="AD136" t="s">
         <v>459</v>
       </c>
-      <c r="AD136" t="s">
+      <c r="AE136" t="s">
+        <v>459</v>
+      </c>
+      <c r="AF136" t="s">
         <v>460</v>
-      </c>
-      <c r="AE136" t="s">
-        <v>460</v>
-      </c>
-      <c r="AF136" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="137" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -13902,22 +13893,22 @@
         <v>20</v>
       </c>
       <c r="B137" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C137" t="s">
         <v>20</v>
       </c>
       <c r="D137" t="s">
+        <v>462</v>
+      </c>
+      <c r="F137" t="s">
+        <v>461</v>
+      </c>
+      <c r="G137" t="s">
         <v>463</v>
       </c>
-      <c r="F137" t="s">
-        <v>462</v>
-      </c>
-      <c r="G137" t="s">
-        <v>464</v>
-      </c>
       <c r="H137" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="I137">
         <v>1</v>
@@ -13926,22 +13917,22 @@
         <v>25</v>
       </c>
       <c r="K137" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M137" t="s">
         <v>26</v>
       </c>
       <c r="N137" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O137" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="T137" t="s">
+        <v>464</v>
+      </c>
+      <c r="U137" t="s">
         <v>465</v>
-      </c>
-      <c r="U137" t="s">
-        <v>466</v>
       </c>
       <c r="AA137">
         <v>2019</v>
@@ -13950,16 +13941,16 @@
         <v>2019</v>
       </c>
       <c r="AC137" s="25" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AD137" t="s">
+        <v>466</v>
+      </c>
+      <c r="AE137" t="s">
+        <v>466</v>
+      </c>
+      <c r="AF137" t="s">
         <v>467</v>
-      </c>
-      <c r="AE137" t="s">
-        <v>467</v>
-      </c>
-      <c r="AF137" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="138" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -13967,22 +13958,22 @@
         <v>20</v>
       </c>
       <c r="B138" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C138" t="s">
         <v>20</v>
       </c>
       <c r="D138" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F138" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G138" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H138" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="I138">
         <v>1</v>
@@ -13991,22 +13982,22 @@
         <v>25</v>
       </c>
       <c r="K138" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M138" t="s">
         <v>26</v>
       </c>
       <c r="N138" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O138" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="T138" t="s">
+        <v>469</v>
+      </c>
+      <c r="U138" t="s">
         <v>470</v>
-      </c>
-      <c r="U138" t="s">
-        <v>471</v>
       </c>
       <c r="AA138">
         <v>2022</v>
@@ -14015,16 +14006,16 @@
         <v>2022</v>
       </c>
       <c r="AC138" s="24" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AD138" t="s">
+        <v>471</v>
+      </c>
+      <c r="AE138" t="s">
+        <v>471</v>
+      </c>
+      <c r="AF138" t="s">
         <v>472</v>
-      </c>
-      <c r="AE138" t="s">
-        <v>472</v>
-      </c>
-      <c r="AF138" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="139" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -14032,22 +14023,22 @@
         <v>88</v>
       </c>
       <c r="B139" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C139" t="s">
         <v>88</v>
       </c>
       <c r="D139" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F139" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="G139" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H139" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I139">
         <v>1</v>
@@ -14056,22 +14047,22 @@
         <v>25</v>
       </c>
       <c r="K139" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M139" t="s">
         <v>26</v>
       </c>
       <c r="N139" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O139" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="T139" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="U139" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AA139">
         <v>2022</v>
@@ -14080,16 +14071,16 @@
         <v>2022</v>
       </c>
       <c r="AC139" s="25" t="s">
+        <v>474</v>
+      </c>
+      <c r="AD139" t="s">
         <v>475</v>
       </c>
-      <c r="AD139" t="s">
+      <c r="AE139" t="s">
+        <v>475</v>
+      </c>
+      <c r="AF139" t="s">
         <v>476</v>
-      </c>
-      <c r="AE139" t="s">
-        <v>476</v>
-      </c>
-      <c r="AF139" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="140" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -14097,22 +14088,22 @@
         <v>135</v>
       </c>
       <c r="B140" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C140" t="s">
         <v>135</v>
       </c>
       <c r="D140" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F140" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G140" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H140" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="I140">
         <v>1</v>
@@ -14121,22 +14112,22 @@
         <v>25</v>
       </c>
       <c r="K140" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="M140" t="s">
         <v>26</v>
       </c>
       <c r="N140" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O140" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="T140" t="s">
+        <v>479</v>
+      </c>
+      <c r="U140" t="s">
         <v>480</v>
-      </c>
-      <c r="U140" t="s">
-        <v>481</v>
       </c>
       <c r="AA140">
         <v>2024</v>
@@ -14145,16 +14136,16 @@
         <v>2024</v>
       </c>
       <c r="AC140" s="24" t="s">
+        <v>481</v>
+      </c>
+      <c r="AD140" t="s">
         <v>482</v>
       </c>
-      <c r="AD140" t="s">
+      <c r="AE140" t="s">
+        <v>482</v>
+      </c>
+      <c r="AF140" t="s">
         <v>483</v>
-      </c>
-      <c r="AE140" t="s">
-        <v>483</v>
-      </c>
-      <c r="AF140" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="141" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -14162,22 +14153,22 @@
         <v>172</v>
       </c>
       <c r="B141" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C141" t="s">
         <v>172</v>
       </c>
       <c r="D141" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F141" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G141" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H141" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="I141">
         <v>1</v>
@@ -14186,22 +14177,22 @@
         <v>25</v>
       </c>
       <c r="K141" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="M141" t="s">
         <v>26</v>
       </c>
       <c r="N141" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O141" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="T141" t="s">
+        <v>487</v>
+      </c>
+      <c r="U141" t="s">
         <v>488</v>
-      </c>
-      <c r="U141" t="s">
-        <v>489</v>
       </c>
       <c r="AA141">
         <v>2024</v>
@@ -14210,39 +14201,39 @@
         <v>2024</v>
       </c>
       <c r="AC141" s="25" t="s">
+        <v>489</v>
+      </c>
+      <c r="AD141" t="s">
         <v>490</v>
       </c>
-      <c r="AD141" t="s">
+      <c r="AE141" t="s">
+        <v>490</v>
+      </c>
+      <c r="AF141" t="s">
         <v>491</v>
-      </c>
-      <c r="AE141" t="s">
-        <v>491</v>
-      </c>
-      <c r="AF141" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="142" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B142" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C142" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D142" t="s">
+        <v>492</v>
+      </c>
+      <c r="F142" t="s">
+        <v>492</v>
+      </c>
+      <c r="G142" t="s">
         <v>493</v>
       </c>
-      <c r="F142" t="s">
-        <v>493</v>
-      </c>
-      <c r="G142" t="s">
-        <v>494</v>
-      </c>
       <c r="H142" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="I142">
         <v>1</v>
@@ -14251,22 +14242,22 @@
         <v>25</v>
       </c>
       <c r="K142" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="M142" t="s">
         <v>26</v>
       </c>
       <c r="N142" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O142" t="s">
         <v>35</v>
       </c>
       <c r="T142" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="U142" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AA142">
         <v>2018</v>
@@ -14275,16 +14266,16 @@
         <v>2018</v>
       </c>
       <c r="AC142" s="24" t="s">
+        <v>496</v>
+      </c>
+      <c r="AD142" t="s">
         <v>497</v>
       </c>
-      <c r="AD142" t="s">
+      <c r="AE142" t="s">
+        <v>497</v>
+      </c>
+      <c r="AF142" t="s">
         <v>498</v>
-      </c>
-      <c r="AE142" t="s">
-        <v>498</v>
-      </c>
-      <c r="AF142" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="143" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -14292,22 +14283,22 @@
         <v>129</v>
       </c>
       <c r="B143" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C143" t="s">
         <v>129</v>
       </c>
       <c r="D143" t="s">
+        <v>499</v>
+      </c>
+      <c r="F143" t="s">
+        <v>499</v>
+      </c>
+      <c r="G143" t="s">
         <v>500</v>
       </c>
-      <c r="F143" t="s">
-        <v>500</v>
-      </c>
-      <c r="G143" t="s">
-        <v>501</v>
-      </c>
       <c r="H143" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="I143">
         <v>1</v>
@@ -14316,22 +14307,22 @@
         <v>25</v>
       </c>
       <c r="K143" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="M143" t="s">
         <v>26</v>
       </c>
       <c r="N143" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O143" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="T143" t="s">
+        <v>502</v>
+      </c>
+      <c r="U143" t="s">
         <v>503</v>
-      </c>
-      <c r="U143" t="s">
-        <v>504</v>
       </c>
       <c r="AA143">
         <v>2024</v>
@@ -14340,16 +14331,16 @@
         <v>2024</v>
       </c>
       <c r="AC143" s="25" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AD143" t="s">
+        <v>504</v>
+      </c>
+      <c r="AE143" t="s">
+        <v>504</v>
+      </c>
+      <c r="AF143" t="s">
         <v>505</v>
-      </c>
-      <c r="AE143" t="s">
-        <v>505</v>
-      </c>
-      <c r="AF143" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="144" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -14357,25 +14348,25 @@
         <v>172</v>
       </c>
       <c r="B144" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C144" t="s">
         <v>172</v>
       </c>
       <c r="D144" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E144" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="F144" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="G144" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H144" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="I144">
         <v>1</v>
@@ -14384,22 +14375,22 @@
         <v>25</v>
       </c>
       <c r="K144" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="M144" t="s">
         <v>26</v>
       </c>
       <c r="N144" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O144" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="T144" t="s">
+        <v>507</v>
+      </c>
+      <c r="U144" t="s">
         <v>508</v>
-      </c>
-      <c r="U144" t="s">
-        <v>509</v>
       </c>
       <c r="AA144">
         <v>2021</v>
@@ -14408,16 +14399,16 @@
         <v>2021</v>
       </c>
       <c r="AC144" s="24" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AD144" t="s">
+        <v>509</v>
+      </c>
+      <c r="AE144" t="s">
+        <v>509</v>
+      </c>
+      <c r="AF144" t="s">
         <v>510</v>
-      </c>
-      <c r="AE144" t="s">
-        <v>510</v>
-      </c>
-      <c r="AF144" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="145" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -14425,22 +14416,22 @@
         <v>20</v>
       </c>
       <c r="B145" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C145" t="s">
         <v>20</v>
       </c>
       <c r="D145" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F145" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="G145" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H145" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="I145">
         <v>1</v>
@@ -14449,22 +14440,22 @@
         <v>25</v>
       </c>
       <c r="K145" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M145" t="s">
         <v>26</v>
       </c>
       <c r="N145" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O145" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="T145" t="s">
+        <v>512</v>
+      </c>
+      <c r="U145" t="s">
         <v>513</v>
-      </c>
-      <c r="U145" t="s">
-        <v>514</v>
       </c>
       <c r="AA145">
         <v>2021</v>
@@ -14473,16 +14464,16 @@
         <v>2021</v>
       </c>
       <c r="AC145" s="25" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AD145" t="s">
+        <v>514</v>
+      </c>
+      <c r="AE145" t="s">
+        <v>514</v>
+      </c>
+      <c r="AF145" t="s">
         <v>515</v>
-      </c>
-      <c r="AE145" t="s">
-        <v>515</v>
-      </c>
-      <c r="AF145" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="146" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -14490,22 +14481,22 @@
         <v>47</v>
       </c>
       <c r="B146" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C146" t="s">
         <v>47</v>
       </c>
       <c r="D146" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F146" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="G146" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H146" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="I146">
         <v>1</v>
@@ -14514,22 +14505,22 @@
         <v>25</v>
       </c>
       <c r="K146" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="M146" t="s">
         <v>26</v>
       </c>
       <c r="N146" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O146" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="T146" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="U146" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AA146">
         <v>2024</v>
@@ -14538,16 +14529,16 @@
         <v>2024</v>
       </c>
       <c r="AC146" s="24" t="s">
+        <v>519</v>
+      </c>
+      <c r="AD146" t="s">
+        <v>490</v>
+      </c>
+      <c r="AE146" t="s">
+        <v>490</v>
+      </c>
+      <c r="AF146" t="s">
         <v>520</v>
-      </c>
-      <c r="AD146" t="s">
-        <v>491</v>
-      </c>
-      <c r="AE146" t="s">
-        <v>491</v>
-      </c>
-      <c r="AF146" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="147" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -14555,22 +14546,22 @@
         <v>20</v>
       </c>
       <c r="B147" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C147" t="s">
         <v>20</v>
       </c>
       <c r="D147" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F147" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="G147" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H147" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="I147">
         <v>1</v>
@@ -14579,22 +14570,22 @@
         <v>25</v>
       </c>
       <c r="K147" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="M147" t="s">
         <v>26</v>
       </c>
       <c r="N147" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O147" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="T147" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="U147" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AA147">
         <v>2019</v>
@@ -14603,16 +14594,16 @@
         <v>2019</v>
       </c>
       <c r="AC147" s="25" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AD147" t="s">
+        <v>524</v>
+      </c>
+      <c r="AE147" t="s">
+        <v>524</v>
+      </c>
+      <c r="AF147" t="s">
         <v>525</v>
-      </c>
-      <c r="AE147" t="s">
-        <v>525</v>
-      </c>
-      <c r="AF147" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="148" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -14620,25 +14611,25 @@
         <v>172</v>
       </c>
       <c r="B148" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C148" t="s">
         <v>172</v>
       </c>
       <c r="D148" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E148" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="F148" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G148" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H148" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="I148">
         <v>1</v>
@@ -14647,22 +14638,22 @@
         <v>25</v>
       </c>
       <c r="K148" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="M148" t="s">
         <v>26</v>
       </c>
       <c r="N148" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O148" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="T148" t="s">
+        <v>527</v>
+      </c>
+      <c r="U148" t="s">
         <v>528</v>
-      </c>
-      <c r="U148" t="s">
-        <v>529</v>
       </c>
       <c r="AA148">
         <v>2023</v>
@@ -14671,16 +14662,16 @@
         <v>2023</v>
       </c>
       <c r="AC148" s="24" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AD148" t="s">
+        <v>529</v>
+      </c>
+      <c r="AE148" t="s">
+        <v>529</v>
+      </c>
+      <c r="AF148" t="s">
         <v>530</v>
-      </c>
-      <c r="AE148" t="s">
-        <v>530</v>
-      </c>
-      <c r="AF148" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="149" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -14688,22 +14679,22 @@
         <v>20</v>
       </c>
       <c r="B149" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C149" t="s">
         <v>20</v>
       </c>
       <c r="D149" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F149" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="G149" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H149" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="I149">
         <v>1</v>
@@ -14712,22 +14703,22 @@
         <v>25</v>
       </c>
       <c r="K149" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="M149" t="s">
         <v>26</v>
       </c>
       <c r="N149" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O149" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="T149" t="s">
+        <v>532</v>
+      </c>
+      <c r="U149" t="s">
         <v>533</v>
-      </c>
-      <c r="U149" t="s">
-        <v>534</v>
       </c>
       <c r="AA149">
         <v>2019</v>
@@ -14736,16 +14727,16 @@
         <v>2019</v>
       </c>
       <c r="AC149" s="25" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AD149" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AE149" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AF149" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="150" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -14753,22 +14744,22 @@
         <v>88</v>
       </c>
       <c r="B150" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C150" t="s">
         <v>88</v>
       </c>
       <c r="D150" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F150" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="G150" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H150" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="I150">
         <v>1</v>
@@ -14777,22 +14768,22 @@
         <v>25</v>
       </c>
       <c r="K150" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="M150" t="s">
         <v>26</v>
       </c>
       <c r="N150" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O150" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="T150" t="s">
+        <v>536</v>
+      </c>
+      <c r="U150" t="s">
         <v>537</v>
-      </c>
-      <c r="U150" t="s">
-        <v>538</v>
       </c>
       <c r="AA150">
         <v>2023</v>
@@ -14801,16 +14792,16 @@
         <v>2023</v>
       </c>
       <c r="AC150" s="24" t="s">
+        <v>538</v>
+      </c>
+      <c r="AD150" t="s">
         <v>539</v>
       </c>
-      <c r="AD150" t="s">
+      <c r="AE150" t="s">
+        <v>539</v>
+      </c>
+      <c r="AF150" t="s">
         <v>540</v>
-      </c>
-      <c r="AE150" t="s">
-        <v>540</v>
-      </c>
-      <c r="AF150" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="151" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -14818,22 +14809,22 @@
         <v>78</v>
       </c>
       <c r="B151" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C151" t="s">
         <v>78</v>
       </c>
       <c r="D151" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F151" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="G151" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H151" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="I151">
         <v>1</v>
@@ -14842,22 +14833,22 @@
         <v>25</v>
       </c>
       <c r="K151" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="M151" t="s">
         <v>26</v>
       </c>
       <c r="N151" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O151" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="T151" t="s">
+        <v>544</v>
+      </c>
+      <c r="U151" t="s">
         <v>545</v>
-      </c>
-      <c r="U151" t="s">
-        <v>546</v>
       </c>
       <c r="AA151">
         <v>2021</v>
@@ -14866,16 +14857,16 @@
         <v>2021</v>
       </c>
       <c r="AC151" s="25" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AD151" t="s">
+        <v>546</v>
+      </c>
+      <c r="AE151" t="s">
+        <v>546</v>
+      </c>
+      <c r="AF151" t="s">
         <v>547</v>
-      </c>
-      <c r="AE151" t="s">
-        <v>547</v>
-      </c>
-      <c r="AF151" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="152" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -14883,22 +14874,22 @@
         <v>78</v>
       </c>
       <c r="B152" s="22" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C152" t="s">
         <v>78</v>
       </c>
       <c r="D152" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F152" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G152" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H152" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="I152">
         <v>1</v>
@@ -14907,22 +14898,22 @@
         <v>25</v>
       </c>
       <c r="K152" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="M152" t="s">
         <v>26</v>
       </c>
       <c r="N152" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O152" t="s">
         <v>35</v>
       </c>
       <c r="T152" t="s">
+        <v>549</v>
+      </c>
+      <c r="U152" t="s">
         <v>550</v>
-      </c>
-      <c r="U152" t="s">
-        <v>551</v>
       </c>
       <c r="AA152">
         <v>2022</v>
@@ -14931,16 +14922,16 @@
         <v>2022</v>
       </c>
       <c r="AC152" s="25" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AD152" t="s">
+        <v>551</v>
+      </c>
+      <c r="AE152" t="s">
+        <v>551</v>
+      </c>
+      <c r="AF152" t="s">
         <v>552</v>
-      </c>
-      <c r="AE152" t="s">
-        <v>552</v>
-      </c>
-      <c r="AF152" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="153" spans="1:32" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">

--- a/scripts/data/Quality_parameters_v15042026.xlsx
+++ b/scripts/data/Quality_parameters_v15042026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daan\Documents\GitHub\Website_Open_Topography_EU\scripts\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE7D7B2-9169-4233-B469-8D6490F53BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1AA27D-C789-485B-A38A-BD6B8096C090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{4BC1C8BB-35EF-4D62-B165-EB1ACD4AD7A7}"/>
+    <workbookView xWindow="4920" yWindow="3255" windowWidth="28800" windowHeight="15240" xr2:uid="{4BC1C8BB-35EF-4D62-B165-EB1ACD4AD7A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Quality_parameters_v12032026" sheetId="1" r:id="rId1"/>
